--- a/research/traditional_assets/database/data/slovenia/slovenia_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_telecom_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0773956929436591</v>
+        <v>0.07728509112706615</v>
       </c>
       <c r="C2">
-        <v>998.2685148222644</v>
+        <v>989.836824637256</v>
       </c>
       <c r="D2">
-        <v>947.4685148222644</v>
+        <v>948.769824637256</v>
       </c>
       <c r="E2">
-        <v>-458.6</v>
+        <v>-448.867</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.733000000000001</v>
       </c>
       <c r="G2">
         <v>50.8</v>
@@ -1451,28 +1451,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4895699</v>
       </c>
       <c r="N2">
-        <v>55.34999999999999</v>
+        <v>54.86043009999999</v>
       </c>
       <c r="O2">
-        <v>10.5165</v>
+        <v>10.423481719</v>
       </c>
       <c r="P2">
-        <v>44.83349999999999</v>
+        <v>44.43694838099999</v>
       </c>
       <c r="Q2">
-        <v>230.7335</v>
+        <v>230.336948381</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0773956929436591</v>
+        <v>0.07765420315865268</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5371076276914757</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>113.0584212795762</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07728509112706615</v>
+        <v>0.0771744893104732</v>
       </c>
       <c r="C3">
-        <v>989.836824637256</v>
+        <v>981.408713961716</v>
       </c>
       <c r="D3">
-        <v>948.769824637256</v>
+        <v>950.074713961716</v>
       </c>
       <c r="E3">
-        <v>-448.867</v>
+        <v>-439.134</v>
       </c>
       <c r="F3">
-        <v>9.733000000000001</v>
+        <v>19.466</v>
       </c>
       <c r="G3">
         <v>50.8</v>
@@ -1533,28 +1533,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M3">
-        <v>0.4895699</v>
+        <v>0.9791398</v>
       </c>
       <c r="N3">
-        <v>54.86043009999999</v>
+        <v>54.3708602</v>
       </c>
       <c r="O3">
-        <v>10.423481719</v>
+        <v>10.330463438</v>
       </c>
       <c r="P3">
-        <v>44.43694838099999</v>
+        <v>44.040396762</v>
       </c>
       <c r="Q3">
-        <v>230.336948381</v>
+        <v>229.940396762</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07765420315865268</v>
+        <v>0.07791798909231959</v>
       </c>
       <c r="T3">
-        <v>0.5371076276914757</v>
+        <v>0.5415554374936722</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>113.0584212795762</v>
+        <v>56.5292106397881</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0771744893104732</v>
+        <v>0.07706388749388024</v>
       </c>
       <c r="C4">
-        <v>981.408713961716</v>
+        <v>972.9841975852064</v>
       </c>
       <c r="D4">
-        <v>950.074713961716</v>
+        <v>951.3831975852064</v>
       </c>
       <c r="E4">
-        <v>-439.134</v>
+        <v>-429.401</v>
       </c>
       <c r="F4">
-        <v>19.466</v>
+        <v>29.199</v>
       </c>
       <c r="G4">
         <v>50.8</v>
@@ -1615,28 +1615,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M4">
-        <v>0.9791398</v>
+        <v>1.4687097</v>
       </c>
       <c r="N4">
-        <v>54.3708602</v>
+        <v>53.8812903</v>
       </c>
       <c r="O4">
-        <v>10.330463438</v>
+        <v>10.237445157</v>
       </c>
       <c r="P4">
-        <v>44.040396762</v>
+        <v>43.64384514299999</v>
       </c>
       <c r="Q4">
-        <v>229.940396762</v>
+        <v>229.543845143</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07791798909231959</v>
+        <v>0.07818721391121675</v>
       </c>
       <c r="T4">
-        <v>0.5415554374936722</v>
+        <v>0.5460949547144708</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>56.5292106397881</v>
+        <v>37.68614042652541</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07706388749388024</v>
+        <v>0.07695328567728729</v>
       </c>
       <c r="C5">
-        <v>972.9841975852064</v>
+        <v>964.5632903788763</v>
       </c>
       <c r="D5">
-        <v>951.3831975852064</v>
+        <v>952.6952903788764</v>
       </c>
       <c r="E5">
-        <v>-429.401</v>
+        <v>-419.668</v>
       </c>
       <c r="F5">
-        <v>29.199</v>
+        <v>38.932</v>
       </c>
       <c r="G5">
         <v>50.8</v>
@@ -1697,28 +1697,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M5">
-        <v>1.4687097</v>
+        <v>1.9582796</v>
       </c>
       <c r="N5">
-        <v>53.8812903</v>
+        <v>53.3917204</v>
       </c>
       <c r="O5">
-        <v>10.237445157</v>
+        <v>10.144426876</v>
       </c>
       <c r="P5">
-        <v>43.64384514299999</v>
+        <v>43.247293524</v>
       </c>
       <c r="Q5">
-        <v>229.543845143</v>
+        <v>229.147293524</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07818721391121675</v>
+        <v>0.07846204758050759</v>
       </c>
       <c r="T5">
-        <v>0.5460949547144708</v>
+        <v>0.5507290452107025</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>37.68614042652541</v>
+        <v>28.26460531989405</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07695328567728729</v>
+        <v>0.07684268386069432</v>
       </c>
       <c r="C6">
-        <v>964.5632903788763</v>
+        <v>956.1460072960265</v>
       </c>
       <c r="D6">
-        <v>952.6952903788764</v>
+        <v>954.0110072960265</v>
       </c>
       <c r="E6">
-        <v>-419.668</v>
+        <v>-409.935</v>
       </c>
       <c r="F6">
-        <v>38.932</v>
+        <v>48.66500000000001</v>
       </c>
       <c r="G6">
         <v>50.8</v>
@@ -1779,28 +1779,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M6">
-        <v>1.9582796</v>
+        <v>2.4478495</v>
       </c>
       <c r="N6">
-        <v>53.3917204</v>
+        <v>52.90215049999999</v>
       </c>
       <c r="O6">
-        <v>10.144426876</v>
+        <v>10.051408595</v>
       </c>
       <c r="P6">
-        <v>43.247293524</v>
+        <v>42.85074190499999</v>
       </c>
       <c r="Q6">
-        <v>229.147293524</v>
+        <v>228.750741905</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07846204758050759</v>
+        <v>0.0787426672217835</v>
       </c>
       <c r="T6">
-        <v>0.5507290452107025</v>
+        <v>0.5554606955068551</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>28.26460531989405</v>
+        <v>22.61168425591524</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07684268386069432</v>
+        <v>0.07673208204410138</v>
       </c>
       <c r="C7">
-        <v>956.1460072960265</v>
+        <v>947.7323633726752</v>
       </c>
       <c r="D7">
-        <v>954.0110072960265</v>
+        <v>955.3303633726753</v>
       </c>
       <c r="E7">
-        <v>-409.935</v>
+        <v>-400.202</v>
       </c>
       <c r="F7">
-        <v>48.66500000000001</v>
+        <v>58.39800000000001</v>
       </c>
       <c r="G7">
         <v>50.8</v>
@@ -1861,28 +1861,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M7">
-        <v>2.4478495</v>
+        <v>2.9374194</v>
       </c>
       <c r="N7">
-        <v>52.90215049999999</v>
+        <v>52.41258059999999</v>
       </c>
       <c r="O7">
-        <v>10.051408595</v>
+        <v>9.958390313999999</v>
       </c>
       <c r="P7">
-        <v>42.85074190499999</v>
+        <v>42.45419028599999</v>
       </c>
       <c r="Q7">
-        <v>228.750741905</v>
+        <v>228.354190286</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0787426672217835</v>
+        <v>0.07902925749372487</v>
       </c>
       <c r="T7">
-        <v>0.5554606955068551</v>
+        <v>0.5602930192135641</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>22.61168425591524</v>
+        <v>18.8430702132627</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07673208204410138</v>
+        <v>0.07662148022750843</v>
       </c>
       <c r="C8">
-        <v>947.7323633726752</v>
+        <v>939.3223737281346</v>
       </c>
       <c r="D8">
-        <v>955.3303633726753</v>
+        <v>956.6533737281346</v>
       </c>
       <c r="E8">
-        <v>-400.202</v>
+        <v>-390.4690000000001</v>
       </c>
       <c r="F8">
-        <v>58.398</v>
+        <v>68.131</v>
       </c>
       <c r="G8">
         <v>50.8</v>
@@ -1943,28 +1943,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M8">
-        <v>2.9374194</v>
+        <v>3.4269893</v>
       </c>
       <c r="N8">
-        <v>52.41258059999999</v>
+        <v>51.92301069999999</v>
       </c>
       <c r="O8">
-        <v>9.958390313999999</v>
+        <v>9.865372032999998</v>
       </c>
       <c r="P8">
-        <v>42.45419028599999</v>
+        <v>42.05763866699999</v>
       </c>
       <c r="Q8">
-        <v>228.354190286</v>
+        <v>227.957638667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07902925749372487</v>
+        <v>0.07932201099732089</v>
       </c>
       <c r="T8">
-        <v>0.5602930192135641</v>
+        <v>0.5652292638602023</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>18.8430702132627</v>
+        <v>16.15120303993946</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07662148022750842</v>
+        <v>0.0765108784109155</v>
       </c>
       <c r="C9">
-        <v>939.3223737281348</v>
+        <v>930.9160535655851</v>
       </c>
       <c r="D9">
-        <v>956.6533737281349</v>
+        <v>957.9800535655852</v>
       </c>
       <c r="E9">
-        <v>-390.469</v>
+        <v>-380.736</v>
       </c>
       <c r="F9">
-        <v>68.13100000000001</v>
+        <v>77.864</v>
       </c>
       <c r="G9">
         <v>50.8</v>
@@ -2025,28 +2025,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M9">
-        <v>3.426989300000001</v>
+        <v>3.9165592</v>
       </c>
       <c r="N9">
-        <v>51.92301069999999</v>
+        <v>51.43344079999999</v>
       </c>
       <c r="O9">
-        <v>9.865372032999998</v>
+        <v>9.772353751999999</v>
       </c>
       <c r="P9">
-        <v>42.05763866699999</v>
+        <v>41.66108704799999</v>
       </c>
       <c r="Q9">
-        <v>227.957638667</v>
+        <v>227.561087048</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07932201099732089</v>
+        <v>0.07962112870751684</v>
       </c>
       <c r="T9">
-        <v>0.5652292638602023</v>
+        <v>0.5702728181730718</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.15120303993945</v>
+        <v>14.13230265994702</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0765108784109155</v>
+        <v>0.07650962659432252</v>
       </c>
       <c r="C10">
-        <v>930.9160535655851</v>
+        <v>921.1980902902856</v>
       </c>
       <c r="D10">
-        <v>957.9800535655852</v>
+        <v>957.9950902902856</v>
       </c>
       <c r="E10">
-        <v>-380.736</v>
+        <v>-371.003</v>
       </c>
       <c r="F10">
-        <v>77.864</v>
+        <v>87.59700000000001</v>
       </c>
       <c r="G10">
         <v>50.8</v>
@@ -2107,45 +2107,45 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M10">
-        <v>3.9165592</v>
+        <v>4.5375246</v>
       </c>
       <c r="N10">
-        <v>51.43344079999999</v>
+        <v>50.8124754</v>
       </c>
       <c r="O10">
-        <v>9.772353751999999</v>
+        <v>9.654370325999999</v>
       </c>
       <c r="P10">
-        <v>41.66108704799999</v>
+        <v>41.158105074</v>
       </c>
       <c r="Q10">
-        <v>227.561087048</v>
+        <v>227.058105074</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07962112870751684</v>
+        <v>0.07992682043332144</v>
       </c>
       <c r="T10">
-        <v>0.5702728181730718</v>
+        <v>0.5754272198334768</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.19</v>
       </c>
       <c r="W10">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>14.13230265994702</v>
+        <v>12.19828097460893</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07650962659432252</v>
+        <v>0.07641117477772957</v>
       </c>
       <c r="C11">
-        <v>921.1980902902856</v>
+        <v>912.649166210313</v>
       </c>
       <c r="D11">
-        <v>957.9950902902856</v>
+        <v>959.179166210313</v>
       </c>
       <c r="E11">
-        <v>-371.003</v>
+        <v>-361.27</v>
       </c>
       <c r="F11">
-        <v>87.59700000000001</v>
+        <v>97.33</v>
       </c>
       <c r="G11">
         <v>50.8</v>
@@ -2189,28 +2189,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M11">
-        <v>4.5375246</v>
+        <v>5.041694</v>
       </c>
       <c r="N11">
-        <v>50.8124754</v>
+        <v>50.30830599999999</v>
       </c>
       <c r="O11">
-        <v>9.654370325999999</v>
+        <v>9.55857814</v>
       </c>
       <c r="P11">
-        <v>41.158105074</v>
+        <v>40.74972785999999</v>
       </c>
       <c r="Q11">
-        <v>227.058105074</v>
+        <v>226.64972786</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07992682043332144</v>
+        <v>0.08023930530858842</v>
       </c>
       <c r="T11">
-        <v>0.5754272198334768</v>
+        <v>0.580696163753002</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>12.19828097460893</v>
+        <v>10.97845287714804</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07641117477772957</v>
+        <v>0.07631272296113663</v>
       </c>
       <c r="C12">
-        <v>912.649166210313</v>
+        <v>904.1031727734105</v>
       </c>
       <c r="D12">
-        <v>959.179166210313</v>
+        <v>960.3661727734105</v>
       </c>
       <c r="E12">
-        <v>-361.27</v>
+        <v>-351.537</v>
       </c>
       <c r="F12">
-        <v>97.33000000000001</v>
+        <v>107.063</v>
       </c>
       <c r="G12">
         <v>50.8</v>
@@ -2271,28 +2271,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M12">
-        <v>5.041694000000001</v>
+        <v>5.5458634</v>
       </c>
       <c r="N12">
-        <v>50.30830599999999</v>
+        <v>49.80413659999999</v>
       </c>
       <c r="O12">
-        <v>9.55857814</v>
+        <v>9.462785953999999</v>
       </c>
       <c r="P12">
-        <v>40.74972785999999</v>
+        <v>40.341350646</v>
       </c>
       <c r="Q12">
-        <v>226.64972786</v>
+        <v>226.241350646</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08023930530858842</v>
+        <v>0.08055881231588384</v>
       </c>
       <c r="T12">
-        <v>0.580696163753002</v>
+        <v>0.5860835109066738</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>10.97845287714803</v>
+        <v>9.980411706498215</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07631272296113663</v>
+        <v>0.07637951114454367</v>
       </c>
       <c r="C13">
-        <v>904.1031727734105</v>
+        <v>893.564605730569</v>
       </c>
       <c r="D13">
-        <v>960.3661727734105</v>
+        <v>959.5606057305691</v>
       </c>
       <c r="E13">
-        <v>-351.537</v>
+        <v>-341.804</v>
       </c>
       <c r="F13">
-        <v>107.063</v>
+        <v>116.796</v>
       </c>
       <c r="G13">
         <v>50.8</v>
@@ -2353,45 +2353,45 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M13">
-        <v>5.5458634</v>
+        <v>6.248586</v>
       </c>
       <c r="N13">
-        <v>49.80413659999999</v>
+        <v>49.10141399999999</v>
       </c>
       <c r="O13">
-        <v>9.462785953999999</v>
+        <v>9.329268659999999</v>
       </c>
       <c r="P13">
-        <v>40.341350646</v>
+        <v>39.77214533999999</v>
       </c>
       <c r="Q13">
-        <v>226.241350646</v>
+        <v>225.67214534</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08055881231588384</v>
+        <v>0.08088558084607235</v>
       </c>
       <c r="T13">
-        <v>0.5860835109066738</v>
+        <v>0.5915932977683835</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.19</v>
       </c>
       <c r="W13">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>9.980411706498215</v>
+        <v>8.858004034832838</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07637951114454367</v>
+        <v>0.07629482932795072</v>
       </c>
       <c r="C14">
-        <v>893.564605730569</v>
+        <v>884.8532269798799</v>
       </c>
       <c r="D14">
-        <v>959.5606057305691</v>
+        <v>960.5822269798799</v>
       </c>
       <c r="E14">
-        <v>-341.804</v>
+        <v>-332.071</v>
       </c>
       <c r="F14">
-        <v>116.796</v>
+        <v>126.529</v>
       </c>
       <c r="G14">
         <v>50.8</v>
@@ -2435,28 +2435,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M14">
-        <v>6.248586</v>
+        <v>6.7693015</v>
       </c>
       <c r="N14">
-        <v>49.10141399999999</v>
+        <v>48.5806985</v>
       </c>
       <c r="O14">
-        <v>9.329268659999999</v>
+        <v>9.230332714999999</v>
       </c>
       <c r="P14">
-        <v>39.77214533999999</v>
+        <v>39.35036578499999</v>
       </c>
       <c r="Q14">
-        <v>225.67214534</v>
+        <v>225.250365785</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08088558084607235</v>
+        <v>0.08121986129649508</v>
       </c>
       <c r="T14">
-        <v>0.5915932977683835</v>
+        <v>0.5972297463970293</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.858004034832838</v>
+        <v>8.176619109076467</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07629482932795072</v>
+        <v>0.07630086751135776</v>
       </c>
       <c r="C15">
-        <v>884.8532269798799</v>
+        <v>875.0473089006334</v>
       </c>
       <c r="D15">
-        <v>960.5822269798799</v>
+        <v>960.5093089006335</v>
       </c>
       <c r="E15">
-        <v>-332.071</v>
+        <v>-322.338</v>
       </c>
       <c r="F15">
-        <v>126.529</v>
+        <v>136.262</v>
       </c>
       <c r="G15">
         <v>50.8</v>
@@ -2517,45 +2517,45 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M15">
-        <v>6.7693015</v>
+        <v>7.399026600000002</v>
       </c>
       <c r="N15">
-        <v>48.5806985</v>
+        <v>47.9509734</v>
       </c>
       <c r="O15">
-        <v>9.230332714999999</v>
+        <v>9.110684945999999</v>
       </c>
       <c r="P15">
-        <v>39.35036578499999</v>
+        <v>38.840288454</v>
       </c>
       <c r="Q15">
-        <v>225.250365785</v>
+        <v>224.740288454</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08121986129649508</v>
+        <v>0.08156191571088112</v>
       </c>
       <c r="T15">
-        <v>0.5972297463970293</v>
+        <v>0.6029972752263412</v>
       </c>
       <c r="U15">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V15">
         <v>0.19</v>
       </c>
       <c r="W15">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.176619109076467</v>
+        <v>7.480713746859618</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07630086751135776</v>
+        <v>0.07622266569476481</v>
       </c>
       <c r="C16">
-        <v>875.0473089006334</v>
+        <v>866.2595442855106</v>
       </c>
       <c r="D16">
-        <v>960.5093089006335</v>
+        <v>961.4545442855107</v>
       </c>
       <c r="E16">
-        <v>-322.338</v>
+        <v>-312.605</v>
       </c>
       <c r="F16">
-        <v>136.262</v>
+        <v>145.995</v>
       </c>
       <c r="G16">
         <v>50.8</v>
@@ -2599,28 +2599,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M16">
-        <v>7.399026600000002</v>
+        <v>7.927528500000002</v>
       </c>
       <c r="N16">
-        <v>47.9509734</v>
+        <v>47.42247149999999</v>
       </c>
       <c r="O16">
-        <v>9.110684945999999</v>
+        <v>9.010269585</v>
       </c>
       <c r="P16">
-        <v>38.840288454</v>
+        <v>38.412201915</v>
       </c>
       <c r="Q16">
-        <v>224.740288454</v>
+        <v>224.312201915</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08156191571088112</v>
+        <v>0.08191201846442919</v>
       </c>
       <c r="T16">
-        <v>0.6029972752263412</v>
+        <v>0.6089005106163426</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.480713746859618</v>
+        <v>6.981999497068977</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07622266569476481</v>
+        <v>0.07614446387817186</v>
       </c>
       <c r="C17">
-        <v>866.2595442855106</v>
+        <v>857.4736419117066</v>
       </c>
       <c r="D17">
-        <v>961.4545442855107</v>
+        <v>962.4016419117066</v>
       </c>
       <c r="E17">
-        <v>-312.605</v>
+        <v>-302.872</v>
       </c>
       <c r="F17">
-        <v>145.995</v>
+        <v>155.728</v>
       </c>
       <c r="G17">
         <v>50.8</v>
@@ -2681,28 +2681,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M17">
-        <v>7.9275285</v>
+        <v>8.456030400000001</v>
       </c>
       <c r="N17">
-        <v>47.42247149999999</v>
+        <v>46.89396959999999</v>
       </c>
       <c r="O17">
-        <v>9.010269585</v>
+        <v>8.909854223999998</v>
       </c>
       <c r="P17">
-        <v>38.412201915</v>
+        <v>37.98411537599999</v>
       </c>
       <c r="Q17">
-        <v>224.312201915</v>
+        <v>223.884115376</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08191201846442919</v>
+        <v>0.08227045699782365</v>
       </c>
       <c r="T17">
-        <v>0.6089005106163426</v>
+        <v>0.6149442992299157</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>6.981999497068978</v>
+        <v>6.545624528502167</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07614446387817186</v>
+        <v>0.0760662620615789</v>
       </c>
       <c r="C18">
-        <v>857.4736419117066</v>
+        <v>848.6896072879481</v>
       </c>
       <c r="D18">
-        <v>962.4016419117066</v>
+        <v>963.3506072879482</v>
       </c>
       <c r="E18">
-        <v>-302.872</v>
+        <v>-293.139</v>
       </c>
       <c r="F18">
-        <v>155.728</v>
+        <v>165.461</v>
       </c>
       <c r="G18">
         <v>50.8</v>
@@ -2763,28 +2763,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M18">
-        <v>8.456030400000001</v>
+        <v>8.984532300000001</v>
       </c>
       <c r="N18">
-        <v>46.89396959999999</v>
+        <v>46.3654677</v>
       </c>
       <c r="O18">
-        <v>8.909854223999998</v>
+        <v>8.809438862999999</v>
       </c>
       <c r="P18">
-        <v>37.98411537599999</v>
+        <v>37.556028837</v>
       </c>
       <c r="Q18">
-        <v>223.884115376</v>
+        <v>223.456028837</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08227045699782365</v>
+        <v>0.08263753260431195</v>
       </c>
       <c r="T18">
-        <v>0.6149442992299157</v>
+        <v>0.6211337213040568</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.545624528502167</v>
+        <v>6.160587791531452</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0760662620615789</v>
+        <v>0.07613386024498596</v>
       </c>
       <c r="C19">
-        <v>848.6896072879481</v>
+        <v>838.1362055673385</v>
       </c>
       <c r="D19">
-        <v>963.3506072879482</v>
+        <v>962.5302055673386</v>
       </c>
       <c r="E19">
-        <v>-293.139</v>
+        <v>-283.4059999999999</v>
       </c>
       <c r="F19">
-        <v>165.461</v>
+        <v>175.194</v>
       </c>
       <c r="G19">
         <v>50.8</v>
@@ -2845,45 +2845,45 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M19">
-        <v>8.984532300000001</v>
+        <v>9.688228200000003</v>
       </c>
       <c r="N19">
-        <v>46.3654677</v>
+        <v>45.66177179999999</v>
       </c>
       <c r="O19">
-        <v>8.809438862999999</v>
+        <v>8.675736641999999</v>
       </c>
       <c r="P19">
-        <v>37.556028837</v>
+        <v>36.98603515799999</v>
       </c>
       <c r="Q19">
-        <v>223.456028837</v>
+        <v>222.886035158</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08263753260431195</v>
+        <v>0.08301356127437312</v>
       </c>
       <c r="T19">
-        <v>0.6211337213040568</v>
+        <v>0.6274741048922011</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.19</v>
       </c>
       <c r="W19">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.160587791531452</v>
+        <v>5.713118937475066</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07613386024498596</v>
+        <v>0.07606375842839301</v>
       </c>
       <c r="C20">
-        <v>838.1362055673385</v>
+        <v>829.2540193561181</v>
       </c>
       <c r="D20">
-        <v>962.5302055673386</v>
+        <v>963.3810193561181</v>
       </c>
       <c r="E20">
-        <v>-283.406</v>
+        <v>-273.673</v>
       </c>
       <c r="F20">
-        <v>175.194</v>
+        <v>184.927</v>
       </c>
       <c r="G20">
         <v>50.8</v>
@@ -2927,28 +2927,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M20">
-        <v>9.688228200000001</v>
+        <v>10.2264631</v>
       </c>
       <c r="N20">
-        <v>45.6617718</v>
+        <v>45.12353689999999</v>
       </c>
       <c r="O20">
-        <v>8.675736641999999</v>
+        <v>8.573472010999998</v>
       </c>
       <c r="P20">
-        <v>36.986035158</v>
+        <v>36.55006488899999</v>
       </c>
       <c r="Q20">
-        <v>222.886035158</v>
+        <v>222.450064889</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08301356127437312</v>
+        <v>0.08339887460295432</v>
       </c>
       <c r="T20">
-        <v>0.6274741048922011</v>
+        <v>0.6339710411615342</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.713118937475068</v>
+        <v>5.412428467081643</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07606375842839301</v>
+        <v>0.07599365661180005</v>
       </c>
       <c r="C21">
-        <v>829.2540193561181</v>
+        <v>820.3733386031813</v>
       </c>
       <c r="D21">
-        <v>963.3810193561181</v>
+        <v>964.2333386031813</v>
       </c>
       <c r="E21">
-        <v>-273.673</v>
+        <v>-263.94</v>
       </c>
       <c r="F21">
-        <v>184.927</v>
+        <v>194.66</v>
       </c>
       <c r="G21">
         <v>50.8</v>
@@ -3009,28 +3009,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M21">
-        <v>10.2264631</v>
+        <v>10.764698</v>
       </c>
       <c r="N21">
-        <v>45.12353689999999</v>
+        <v>44.58530199999999</v>
       </c>
       <c r="O21">
-        <v>8.573472010999998</v>
+        <v>8.471207379999999</v>
       </c>
       <c r="P21">
-        <v>36.55006488899999</v>
+        <v>36.11409461999999</v>
       </c>
       <c r="Q21">
-        <v>222.450064889</v>
+        <v>222.01409462</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08339887460295432</v>
+        <v>0.08379382076475006</v>
       </c>
       <c r="T21">
-        <v>0.6339710411615342</v>
+        <v>0.6406304008376009</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.412428467081643</v>
+        <v>5.141807043727561</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07599365661180005</v>
+        <v>0.0759235547952071</v>
       </c>
       <c r="C22">
-        <v>820.3733386031813</v>
+        <v>811.4941673077781</v>
       </c>
       <c r="D22">
-        <v>964.2333386031813</v>
+        <v>965.0871673077781</v>
       </c>
       <c r="E22">
-        <v>-263.94</v>
+        <v>-254.207</v>
       </c>
       <c r="F22">
-        <v>194.66</v>
+        <v>204.393</v>
       </c>
       <c r="G22">
         <v>50.8</v>
@@ -3091,28 +3091,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M22">
-        <v>10.764698</v>
+        <v>11.3029329</v>
       </c>
       <c r="N22">
-        <v>44.58530199999999</v>
+        <v>44.04706709999999</v>
       </c>
       <c r="O22">
-        <v>8.471207379999999</v>
+        <v>8.368942748999999</v>
       </c>
       <c r="P22">
-        <v>36.11409461999999</v>
+        <v>35.67812435099999</v>
       </c>
       <c r="Q22">
-        <v>222.01409462</v>
+        <v>221.578124351</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08379382076475006</v>
+        <v>0.0841987655635533</v>
       </c>
       <c r="T22">
-        <v>0.6406304008376009</v>
+        <v>0.6474583518978716</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.141807043727561</v>
+        <v>4.896959089264343</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0759235547952071</v>
+        <v>0.07585345297861414</v>
       </c>
       <c r="C23">
-        <v>811.4941673077781</v>
+        <v>802.616509483337</v>
       </c>
       <c r="D23">
-        <v>965.0871673077781</v>
+        <v>965.9425094833371</v>
       </c>
       <c r="E23">
-        <v>-254.207</v>
+        <v>-244.474</v>
       </c>
       <c r="F23">
-        <v>204.393</v>
+        <v>214.126</v>
       </c>
       <c r="G23">
         <v>50.8</v>
@@ -3173,28 +3173,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M23">
-        <v>11.3029329</v>
+        <v>11.8411678</v>
       </c>
       <c r="N23">
-        <v>44.04706709999999</v>
+        <v>43.50883219999999</v>
       </c>
       <c r="O23">
-        <v>8.368942748999999</v>
+        <v>8.266678117999998</v>
       </c>
       <c r="P23">
-        <v>35.67812435099999</v>
+        <v>35.242154082</v>
       </c>
       <c r="Q23">
-        <v>221.578124351</v>
+        <v>221.142154082</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.0841987655635533</v>
+        <v>0.08461409356232583</v>
       </c>
       <c r="T23">
-        <v>0.6474583518978716</v>
+        <v>0.6544613786263545</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.896959089264344</v>
+        <v>4.674370039752328</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07585345297861414</v>
+        <v>0.07624910116202119</v>
       </c>
       <c r="C24">
-        <v>802.616509483337</v>
+        <v>788.075807320879</v>
       </c>
       <c r="D24">
-        <v>965.9425094833371</v>
+        <v>961.1348073208791</v>
       </c>
       <c r="E24">
-        <v>-244.474</v>
+        <v>-234.741</v>
       </c>
       <c r="F24">
-        <v>214.126</v>
+        <v>223.859</v>
       </c>
       <c r="G24">
         <v>50.8</v>
@@ -3255,45 +3255,45 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M24">
-        <v>11.8411678</v>
+        <v>12.9390502</v>
       </c>
       <c r="N24">
-        <v>43.50883219999999</v>
+        <v>42.41094979999999</v>
       </c>
       <c r="O24">
-        <v>8.266678117999998</v>
+        <v>8.058080461999998</v>
       </c>
       <c r="P24">
-        <v>35.242154082</v>
+        <v>34.35286933799999</v>
       </c>
       <c r="Q24">
-        <v>221.142154082</v>
+        <v>220.252869338</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08461409356232583</v>
+        <v>0.08504020930132622</v>
       </c>
       <c r="T24">
-        <v>0.6544613786263545</v>
+        <v>0.6616463021529796</v>
       </c>
       <c r="U24">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V24">
         <v>0.19</v>
       </c>
       <c r="W24">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.674370039752328</v>
+        <v>4.277748300257771</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07624910116202119</v>
+        <v>0.07619924934542825</v>
       </c>
       <c r="C25">
-        <v>788.075807320879</v>
+        <v>778.9459427481411</v>
       </c>
       <c r="D25">
-        <v>961.1348073208791</v>
+        <v>961.7379427481411</v>
       </c>
       <c r="E25">
-        <v>-234.741</v>
+        <v>-225.008</v>
       </c>
       <c r="F25">
-        <v>223.859</v>
+        <v>233.592</v>
       </c>
       <c r="G25">
         <v>50.8</v>
@@ -3337,28 +3337,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M25">
-        <v>12.9390502</v>
+        <v>13.5016176</v>
       </c>
       <c r="N25">
-        <v>42.41094979999999</v>
+        <v>41.84838239999999</v>
       </c>
       <c r="O25">
-        <v>8.058080461999998</v>
+        <v>7.951192655999998</v>
       </c>
       <c r="P25">
-        <v>34.35286933799999</v>
+        <v>33.89718974399999</v>
       </c>
       <c r="Q25">
-        <v>220.252869338</v>
+        <v>219.797189744</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08504020930132622</v>
+        <v>0.08547753861240558</v>
       </c>
       <c r="T25">
-        <v>0.6616463021529796</v>
+        <v>0.6690203026145161</v>
       </c>
       <c r="U25">
         <v>0.0578</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.277748300257771</v>
+        <v>4.099508787747031</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07619924934542824</v>
+        <v>0.07685814752883528</v>
       </c>
       <c r="C26">
-        <v>778.9459427481413</v>
+        <v>761.3018333313355</v>
       </c>
       <c r="D26">
-        <v>961.7379427481413</v>
+        <v>953.8268333313356</v>
       </c>
       <c r="E26">
-        <v>-225.008</v>
+        <v>-215.275</v>
       </c>
       <c r="F26">
-        <v>233.592</v>
+        <v>243.325</v>
       </c>
       <c r="G26">
         <v>50.8</v>
@@ -3419,45 +3419,45 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M26">
-        <v>13.5016176</v>
+        <v>14.9158225</v>
       </c>
       <c r="N26">
-        <v>41.84838239999999</v>
+        <v>40.43417749999999</v>
       </c>
       <c r="O26">
-        <v>7.951192655999998</v>
+        <v>7.682493724999998</v>
       </c>
       <c r="P26">
-        <v>33.89718974399999</v>
+        <v>32.75168377499999</v>
       </c>
       <c r="Q26">
-        <v>219.797189744</v>
+        <v>218.651683775</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08547753861240558</v>
+        <v>0.08592653003844705</v>
       </c>
       <c r="T26">
-        <v>0.6690203026145161</v>
+        <v>0.6765909430883602</v>
       </c>
       <c r="U26">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V26">
         <v>0.19</v>
       </c>
       <c r="W26">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.099508787747032</v>
+        <v>3.710824528784785</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07685814752883528</v>
+        <v>0.07683664571224233</v>
       </c>
       <c r="C27">
-        <v>761.3018333313355</v>
+        <v>751.8249416085781</v>
       </c>
       <c r="D27">
-        <v>953.8268333313356</v>
+        <v>954.0829416085782</v>
       </c>
       <c r="E27">
-        <v>-215.275</v>
+        <v>-205.542</v>
       </c>
       <c r="F27">
-        <v>243.325</v>
+        <v>253.058</v>
       </c>
       <c r="G27">
         <v>50.8</v>
@@ -3501,28 +3501,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M27">
-        <v>14.9158225</v>
+        <v>15.5124554</v>
       </c>
       <c r="N27">
-        <v>40.43417749999999</v>
+        <v>39.83754459999999</v>
       </c>
       <c r="O27">
-        <v>7.682493724999998</v>
+        <v>7.569133473999999</v>
       </c>
       <c r="P27">
-        <v>32.75168377499999</v>
+        <v>32.268411126</v>
       </c>
       <c r="Q27">
-        <v>218.651683775</v>
+        <v>218.168411126</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08592653003844705</v>
+        <v>0.08638765636789505</v>
       </c>
       <c r="T27">
-        <v>0.6765909430883602</v>
+        <v>0.6843661954669027</v>
       </c>
       <c r="U27">
         <v>0.0613</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.710824528784785</v>
+        <v>3.568100508446908</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07683664571224233</v>
+        <v>0.07742750389564937</v>
       </c>
       <c r="C28">
-        <v>751.8249416085781</v>
+        <v>735.1038968626077</v>
       </c>
       <c r="D28">
-        <v>954.0829416085782</v>
+        <v>947.0948968626078</v>
       </c>
       <c r="E28">
-        <v>-205.542</v>
+        <v>-195.809</v>
       </c>
       <c r="F28">
-        <v>253.058</v>
+        <v>262.7910000000001</v>
       </c>
       <c r="G28">
         <v>50.8</v>
@@ -3583,45 +3583,45 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M28">
-        <v>15.5124554</v>
+        <v>16.8449031</v>
       </c>
       <c r="N28">
-        <v>39.83754459999999</v>
+        <v>38.50509689999999</v>
       </c>
       <c r="O28">
-        <v>7.569133473999999</v>
+        <v>7.315968410999998</v>
       </c>
       <c r="P28">
-        <v>32.268411126</v>
+        <v>31.18912848899999</v>
       </c>
       <c r="Q28">
-        <v>218.168411126</v>
+        <v>217.089128489</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08638765636789505</v>
+        <v>0.08686141629541011</v>
       </c>
       <c r="T28">
-        <v>0.6843661954669027</v>
+        <v>0.692354468458556</v>
       </c>
       <c r="U28">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V28">
         <v>0.19</v>
       </c>
       <c r="W28">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.568100508446908</v>
+        <v>3.28586039773657</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07742750389564937</v>
+        <v>0.07742868207905643</v>
       </c>
       <c r="C29">
-        <v>735.1038968626077</v>
+        <v>725.3570648190746</v>
       </c>
       <c r="D29">
-        <v>947.0948968626078</v>
+        <v>947.0810648190746</v>
       </c>
       <c r="E29">
-        <v>-195.809</v>
+        <v>-186.076</v>
       </c>
       <c r="F29">
-        <v>262.7910000000001</v>
+        <v>272.5240000000001</v>
       </c>
       <c r="G29">
         <v>50.8</v>
@@ -3665,28 +3665,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M29">
-        <v>16.8449031</v>
+        <v>17.4687884</v>
       </c>
       <c r="N29">
-        <v>38.50509689999999</v>
+        <v>37.88121159999999</v>
       </c>
       <c r="O29">
-        <v>7.315968410999998</v>
+        <v>7.197430203999997</v>
       </c>
       <c r="P29">
-        <v>31.18912848899999</v>
+        <v>30.68378139599999</v>
       </c>
       <c r="Q29">
-        <v>217.089128489</v>
+        <v>216.583781396</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08686141629541011</v>
+        <v>0.0873483362209117</v>
       </c>
       <c r="T29">
-        <v>0.692354468458556</v>
+        <v>0.7005646379221997</v>
       </c>
       <c r="U29">
         <v>0.0641</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.28586039773657</v>
+        <v>3.168508240674549</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07742868207905643</v>
+        <v>0.07742986026246348</v>
       </c>
       <c r="C30">
-        <v>725.3570648190746</v>
+        <v>715.6102331795614</v>
       </c>
       <c r="D30">
-        <v>947.0810648190746</v>
+        <v>947.0672331795615</v>
       </c>
       <c r="E30">
-        <v>-186.076</v>
+        <v>-176.343</v>
       </c>
       <c r="F30">
-        <v>272.5240000000001</v>
+        <v>282.2570000000001</v>
       </c>
       <c r="G30">
         <v>50.8</v>
@@ -3747,28 +3747,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M30">
-        <v>17.4687884</v>
+        <v>18.09267370000001</v>
       </c>
       <c r="N30">
-        <v>37.88121159999999</v>
+        <v>37.25732629999999</v>
       </c>
       <c r="O30">
-        <v>7.197430203999997</v>
+        <v>7.078891996999998</v>
       </c>
       <c r="P30">
-        <v>30.68378139599999</v>
+        <v>30.17843430299999</v>
       </c>
       <c r="Q30">
-        <v>216.583781396</v>
+        <v>216.078434303</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0873483362209117</v>
+        <v>0.0878489722006528</v>
       </c>
       <c r="T30">
-        <v>0.7005646379221997</v>
+        <v>0.709006079765101</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.168508240674549</v>
+        <v>3.059249335823703</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07742986026246348</v>
+        <v>0.07932643844587052</v>
       </c>
       <c r="C31">
-        <v>715.6102331795614</v>
+        <v>684.1235265576205</v>
       </c>
       <c r="D31">
-        <v>947.0672331795615</v>
+        <v>925.3135265576205</v>
       </c>
       <c r="E31">
-        <v>-176.343</v>
+        <v>-166.61</v>
       </c>
       <c r="F31">
-        <v>282.257</v>
+        <v>291.99</v>
       </c>
       <c r="G31">
         <v>50.8</v>
@@ -3829,45 +3829,45 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M31">
-        <v>18.0926737</v>
+        <v>20.994081</v>
       </c>
       <c r="N31">
-        <v>37.25732629999999</v>
+        <v>34.35591899999999</v>
       </c>
       <c r="O31">
-        <v>7.078891996999998</v>
+        <v>6.527624609999998</v>
       </c>
       <c r="P31">
-        <v>30.17843430299999</v>
+        <v>27.82829439</v>
       </c>
       <c r="Q31">
-        <v>216.078434303</v>
+        <v>213.72829439</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08784897220065278</v>
+        <v>0.08836391206552932</v>
       </c>
       <c r="T31">
-        <v>0.7090060797651009</v>
+        <v>0.7176887056606566</v>
       </c>
       <c r="U31">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V31">
         <v>0.19</v>
       </c>
       <c r="W31">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>3.059249335823703</v>
+        <v>2.636457390061513</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07932643844587052</v>
+        <v>0.07939079662927757</v>
       </c>
       <c r="C32">
-        <v>684.1235265576205</v>
+        <v>673.6698572659998</v>
       </c>
       <c r="D32">
-        <v>925.3135265576205</v>
+        <v>924.5928572659998</v>
       </c>
       <c r="E32">
-        <v>-166.61</v>
+        <v>-156.877</v>
       </c>
       <c r="F32">
-        <v>291.99</v>
+        <v>301.723</v>
       </c>
       <c r="G32">
         <v>50.8</v>
@@ -3911,28 +3911,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M32">
-        <v>20.994081</v>
+        <v>21.6938837</v>
       </c>
       <c r="N32">
-        <v>34.35591899999999</v>
+        <v>33.65611629999999</v>
       </c>
       <c r="O32">
-        <v>6.527624609999998</v>
+        <v>6.394662096999999</v>
       </c>
       <c r="P32">
-        <v>27.82829439</v>
+        <v>27.261454203</v>
       </c>
       <c r="Q32">
-        <v>213.72829439</v>
+        <v>213.161454203</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08836391206552932</v>
+        <v>0.08889377772359069</v>
       </c>
       <c r="T32">
-        <v>0.7176887056606566</v>
+        <v>0.7266230018720253</v>
       </c>
       <c r="U32">
         <v>0.07190000000000001</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.636457390061513</v>
+        <v>2.551410377478883</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07939079662927757</v>
+        <v>0.08046603481268463</v>
       </c>
       <c r="C33">
-        <v>673.6698572659998</v>
+        <v>652.0604823076792</v>
       </c>
       <c r="D33">
-        <v>924.5928572659998</v>
+        <v>912.7164823076793</v>
       </c>
       <c r="E33">
-        <v>-156.877</v>
+        <v>-147.144</v>
       </c>
       <c r="F33">
-        <v>301.723</v>
+        <v>311.456</v>
       </c>
       <c r="G33">
         <v>50.8</v>
@@ -3993,45 +3993,45 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M33">
-        <v>21.6938837</v>
+        <v>23.6083648</v>
       </c>
       <c r="N33">
-        <v>33.65611629999999</v>
+        <v>31.74163519999999</v>
       </c>
       <c r="O33">
-        <v>6.394662096999999</v>
+        <v>6.030910687999998</v>
       </c>
       <c r="P33">
-        <v>27.261454203</v>
+        <v>25.71072451199999</v>
       </c>
       <c r="Q33">
-        <v>213.161454203</v>
+        <v>211.610724512</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08889377772359069</v>
+        <v>0.08943922766571269</v>
       </c>
       <c r="T33">
-        <v>0.7266230018720253</v>
+        <v>0.7358200715013755</v>
       </c>
       <c r="U33">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V33">
         <v>0.19</v>
       </c>
       <c r="W33">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.551410377478883</v>
+        <v>2.34450799404794</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08046603481268463</v>
+        <v>0.08056198299609167</v>
       </c>
       <c r="C34">
-        <v>652.0604823076792</v>
+        <v>641.2825122921142</v>
       </c>
       <c r="D34">
-        <v>912.7164823076793</v>
+        <v>911.6715122921144</v>
       </c>
       <c r="E34">
-        <v>-147.144</v>
+        <v>-137.411</v>
       </c>
       <c r="F34">
-        <v>311.456</v>
+        <v>321.189</v>
       </c>
       <c r="G34">
         <v>50.8</v>
@@ -4075,28 +4075,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M34">
-        <v>23.6083648</v>
+        <v>24.3461262</v>
       </c>
       <c r="N34">
-        <v>31.74163519999999</v>
+        <v>31.00387379999999</v>
       </c>
       <c r="O34">
-        <v>6.030910687999998</v>
+        <v>5.890736021999998</v>
       </c>
       <c r="P34">
-        <v>25.71072451199999</v>
+        <v>25.11313777799999</v>
       </c>
       <c r="Q34">
-        <v>211.610724512</v>
+        <v>211.013137778</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08943922766571269</v>
+        <v>0.09000095969565922</v>
       </c>
       <c r="T34">
-        <v>0.7358200715013755</v>
+        <v>0.7452916805226466</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.34450799404794</v>
+        <v>2.273462297258608</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08056198299609167</v>
+        <v>0.08065793117949871</v>
       </c>
       <c r="C35">
-        <v>641.2825122921142</v>
+        <v>630.5069323146292</v>
       </c>
       <c r="D35">
-        <v>911.6715122921144</v>
+        <v>910.6289323146293</v>
       </c>
       <c r="E35">
-        <v>-137.411</v>
+        <v>-127.678</v>
       </c>
       <c r="F35">
-        <v>321.189</v>
+        <v>330.922</v>
       </c>
       <c r="G35">
         <v>50.8</v>
@@ -4157,28 +4157,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M35">
-        <v>24.3461262</v>
+        <v>25.0838876</v>
       </c>
       <c r="N35">
-        <v>31.00387379999999</v>
+        <v>30.26611239999999</v>
       </c>
       <c r="O35">
-        <v>5.890736021999998</v>
+        <v>5.750561355999999</v>
       </c>
       <c r="P35">
-        <v>25.11313777799999</v>
+        <v>24.51555104399999</v>
       </c>
       <c r="Q35">
-        <v>211.013137778</v>
+        <v>210.415551044</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09000095969565922</v>
+        <v>0.09057971390833139</v>
       </c>
       <c r="T35">
-        <v>0.7452916805226466</v>
+        <v>0.7550503079991078</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.273462297258608</v>
+        <v>2.206595759103943</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08065793117949871</v>
+        <v>0.08075387936290578</v>
       </c>
       <c r="C36">
-        <v>630.5069323146292</v>
+        <v>619.7337341849068</v>
       </c>
       <c r="D36">
-        <v>910.6289323146293</v>
+        <v>909.5887341849068</v>
       </c>
       <c r="E36">
-        <v>-127.678</v>
+        <v>-117.945</v>
       </c>
       <c r="F36">
-        <v>330.922</v>
+        <v>340.655</v>
       </c>
       <c r="G36">
         <v>50.8</v>
@@ -4239,28 +4239,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M36">
-        <v>25.0838876</v>
+        <v>25.821649</v>
       </c>
       <c r="N36">
-        <v>30.26611239999999</v>
+        <v>29.52835099999999</v>
       </c>
       <c r="O36">
-        <v>5.750561355999999</v>
+        <v>5.610386689999999</v>
       </c>
       <c r="P36">
-        <v>24.51555104399999</v>
+        <v>23.91796430999999</v>
       </c>
       <c r="Q36">
-        <v>210.415551044</v>
+        <v>209.81796431</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09057971390833139</v>
+        <v>0.09117627594293196</v>
       </c>
       <c r="T36">
-        <v>0.7550503079991078</v>
+        <v>0.765109200936383</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.206595759103943</v>
+        <v>2.143550165986688</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08075387936290578</v>
+        <v>0.08084982754631281</v>
       </c>
       <c r="C37">
-        <v>619.7337341849068</v>
+        <v>608.9629097500108</v>
       </c>
       <c r="D37">
-        <v>909.5887341849068</v>
+        <v>908.5509097500109</v>
       </c>
       <c r="E37">
-        <v>-117.945</v>
+        <v>-108.2119999999999</v>
       </c>
       <c r="F37">
-        <v>340.655</v>
+        <v>350.3880000000001</v>
       </c>
       <c r="G37">
         <v>50.8</v>
@@ -4321,28 +4321,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M37">
-        <v>25.821649</v>
+        <v>26.55941040000001</v>
       </c>
       <c r="N37">
-        <v>29.52835099999999</v>
+        <v>28.79058959999999</v>
       </c>
       <c r="O37">
-        <v>5.610386689999999</v>
+        <v>5.470212023999998</v>
       </c>
       <c r="P37">
-        <v>23.91796430999999</v>
+        <v>23.32037757599999</v>
       </c>
       <c r="Q37">
-        <v>209.81796431</v>
+        <v>209.220377576</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09117627594293196</v>
+        <v>0.09179148054111377</v>
       </c>
       <c r="T37">
-        <v>0.765109200936383</v>
+        <v>0.7754824342779483</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.143550165986688</v>
+        <v>2.08400710582039</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08084982754631281</v>
+        <v>0.08094577572971987</v>
       </c>
       <c r="C38">
-        <v>608.9629097500108</v>
+        <v>598.194450894171</v>
       </c>
       <c r="D38">
-        <v>908.5509097500109</v>
+        <v>907.5154508941712</v>
       </c>
       <c r="E38">
-        <v>-108.212</v>
+        <v>-98.47899999999998</v>
       </c>
       <c r="F38">
-        <v>350.388</v>
+        <v>360.121</v>
       </c>
       <c r="G38">
         <v>50.8</v>
@@ -4403,28 +4403,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M38">
-        <v>26.5594104</v>
+        <v>27.2971718</v>
       </c>
       <c r="N38">
-        <v>28.79058959999999</v>
+        <v>28.05282819999999</v>
       </c>
       <c r="O38">
-        <v>5.470212023999999</v>
+        <v>5.330037357999998</v>
       </c>
       <c r="P38">
-        <v>23.32037757599999</v>
+        <v>22.72279084199999</v>
       </c>
       <c r="Q38">
-        <v>209.220377576</v>
+        <v>208.622790842</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09179148054111377</v>
+        <v>0.09242621544399979</v>
       </c>
       <c r="T38">
-        <v>0.7754824342779482</v>
+        <v>0.7861849766144837</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.08400710582039</v>
+        <v>2.027682589446867</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08094577572971987</v>
+        <v>0.08541248391312692</v>
       </c>
       <c r="C39">
-        <v>598.194450894171</v>
+        <v>542.7382138952302</v>
       </c>
       <c r="D39">
-        <v>907.5154508941712</v>
+        <v>861.7922138952302</v>
       </c>
       <c r="E39">
-        <v>-98.47899999999998</v>
+        <v>-88.74599999999998</v>
       </c>
       <c r="F39">
-        <v>360.121</v>
+        <v>369.854</v>
       </c>
       <c r="G39">
         <v>50.8</v>
@@ -4485,45 +4485,45 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M39">
-        <v>27.2971718</v>
+        <v>33.28686</v>
       </c>
       <c r="N39">
-        <v>28.05282819999999</v>
+        <v>22.06313999999999</v>
       </c>
       <c r="O39">
-        <v>5.330037357999998</v>
+        <v>4.191996599999998</v>
       </c>
       <c r="P39">
-        <v>22.72279084199999</v>
+        <v>17.87114339999999</v>
       </c>
       <c r="Q39">
-        <v>208.622790842</v>
+        <v>203.7711434</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09242621544399979</v>
+        <v>0.09308142566633373</v>
       </c>
       <c r="T39">
-        <v>0.7861849766144837</v>
+        <v>0.7972327622521979</v>
       </c>
       <c r="U39">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V39">
         <v>0.19</v>
       </c>
       <c r="W39">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.027682589446867</v>
+        <v>1.662818301275638</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08541248391312692</v>
+        <v>0.08562345209653396</v>
       </c>
       <c r="C40">
-        <v>542.7382138952302</v>
+        <v>530.9593221469381</v>
       </c>
       <c r="D40">
-        <v>861.7922138952302</v>
+        <v>859.7463221469382</v>
       </c>
       <c r="E40">
-        <v>-88.74599999999998</v>
+        <v>-79.01299999999998</v>
       </c>
       <c r="F40">
-        <v>369.854</v>
+        <v>379.587</v>
       </c>
       <c r="G40">
         <v>50.8</v>
@@ -4567,28 +4567,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M40">
-        <v>33.28686</v>
+        <v>34.16283</v>
       </c>
       <c r="N40">
-        <v>22.06313999999999</v>
+        <v>21.18716999999999</v>
       </c>
       <c r="O40">
-        <v>4.191996599999998</v>
+        <v>4.025562299999999</v>
       </c>
       <c r="P40">
-        <v>17.87114339999999</v>
+        <v>17.1616077</v>
       </c>
       <c r="Q40">
-        <v>203.7711434</v>
+        <v>203.0616077</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09308142566633373</v>
+        <v>0.09375811819103927</v>
       </c>
       <c r="T40">
-        <v>0.7972327622521979</v>
+        <v>0.808642770369837</v>
       </c>
       <c r="U40">
         <v>0.09</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.662818301275638</v>
+        <v>1.620181934576263</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08562345209653396</v>
+        <v>0.08583442027994101</v>
       </c>
       <c r="C41">
-        <v>530.9593221469381</v>
+        <v>519.1901212724762</v>
       </c>
       <c r="D41">
-        <v>859.7463221469382</v>
+        <v>857.7101212724763</v>
       </c>
       <c r="E41">
-        <v>-79.01299999999998</v>
+        <v>-69.27999999999997</v>
       </c>
       <c r="F41">
-        <v>379.587</v>
+        <v>389.3200000000001</v>
       </c>
       <c r="G41">
         <v>50.8</v>
@@ -4649,28 +4649,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M41">
-        <v>34.16283</v>
+        <v>35.0388</v>
       </c>
       <c r="N41">
-        <v>21.18716999999999</v>
+        <v>20.31119999999999</v>
       </c>
       <c r="O41">
-        <v>4.025562299999999</v>
+        <v>3.859127999999999</v>
       </c>
       <c r="P41">
-        <v>17.1616077</v>
+        <v>16.45207199999999</v>
       </c>
       <c r="Q41">
-        <v>203.0616077</v>
+        <v>202.352072</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09375811819103927</v>
+        <v>0.09445736713323501</v>
       </c>
       <c r="T41">
-        <v>0.808642770369837</v>
+        <v>0.8204331120913974</v>
       </c>
       <c r="U41">
         <v>0.09</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.620181934576263</v>
+        <v>1.579677386211856</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08583442027994101</v>
+        <v>0.08604538846334805</v>
       </c>
       <c r="C42">
-        <v>519.1901212724762</v>
+        <v>507.430542579691</v>
       </c>
       <c r="D42">
-        <v>857.7101212724763</v>
+        <v>855.6835425796911</v>
       </c>
       <c r="E42">
-        <v>-69.27999999999997</v>
+        <v>-59.54699999999997</v>
       </c>
       <c r="F42">
-        <v>389.3200000000001</v>
+        <v>399.0530000000001</v>
       </c>
       <c r="G42">
         <v>50.8</v>
@@ -4731,28 +4731,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M42">
-        <v>35.0388</v>
+        <v>35.91477</v>
       </c>
       <c r="N42">
-        <v>20.31119999999999</v>
+        <v>19.43522999999999</v>
       </c>
       <c r="O42">
-        <v>3.859127999999999</v>
+        <v>3.692693699999998</v>
       </c>
       <c r="P42">
-        <v>16.45207199999999</v>
+        <v>15.74253629999999</v>
       </c>
       <c r="Q42">
-        <v>202.352072</v>
+        <v>201.6425363</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09445736713323501</v>
+        <v>0.09518031942940347</v>
       </c>
       <c r="T42">
-        <v>0.8204331120913974</v>
+        <v>0.8326231264136886</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.579677386211856</v>
+        <v>1.541148669474982</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08604538846334805</v>
+        <v>0.0862563566467551</v>
       </c>
       <c r="C43">
-        <v>507.430542579691</v>
+        <v>495.6805180241161</v>
       </c>
       <c r="D43">
-        <v>855.6835425796911</v>
+        <v>853.6665180241162</v>
       </c>
       <c r="E43">
-        <v>-59.54699999999997</v>
+        <v>-49.81399999999996</v>
       </c>
       <c r="F43">
-        <v>399.0530000000001</v>
+        <v>408.7860000000001</v>
       </c>
       <c r="G43">
         <v>50.8</v>
@@ -4813,28 +4813,28 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M43">
-        <v>35.91477</v>
+        <v>36.79074000000001</v>
       </c>
       <c r="N43">
-        <v>19.43522999999999</v>
+        <v>18.55925999999999</v>
       </c>
       <c r="O43">
-        <v>3.692693699999998</v>
+        <v>3.526259399999998</v>
       </c>
       <c r="P43">
-        <v>15.74253629999999</v>
+        <v>15.03300059999999</v>
       </c>
       <c r="Q43">
-        <v>201.6425363</v>
+        <v>200.9330006</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09518031942940347</v>
+        <v>0.09592820111509501</v>
       </c>
       <c r="T43">
-        <v>0.8326231264136886</v>
+        <v>0.8452334860574383</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.541148669474982</v>
+        <v>1.504454653535101</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08625635664675511</v>
+        <v>0.107695146139338</v>
       </c>
       <c r="C44">
-        <v>495.680518024116</v>
+        <v>320.9762261264589</v>
       </c>
       <c r="D44">
-        <v>853.666518024116</v>
+        <v>688.6952261264589</v>
       </c>
       <c r="E44">
-        <v>-49.81400000000002</v>
+        <v>-40.08100000000002</v>
       </c>
       <c r="F44">
-        <v>408.786</v>
+        <v>418.519</v>
       </c>
       <c r="G44">
         <v>50.8</v>
@@ -4895,45 +4895,45 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M44">
-        <v>36.79074</v>
+        <v>61.43858920000001</v>
       </c>
       <c r="N44">
-        <v>18.55925999999999</v>
+        <v>-6.088589200000015</v>
       </c>
       <c r="O44">
-        <v>3.526259399999999</v>
+        <v>-1.156831948000003</v>
       </c>
       <c r="P44">
-        <v>15.0330006</v>
+        <v>-4.931757252000013</v>
       </c>
       <c r="Q44">
-        <v>200.9330006</v>
+        <v>180.968242748</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09592820111509501</v>
+        <v>0.09715112186145106</v>
       </c>
       <c r="T44">
-        <v>0.8452334860574382</v>
+        <v>0.8658536867153717</v>
       </c>
       <c r="U44">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V44">
-        <v>0.19</v>
+        <v>0.1711709226552356</v>
       </c>
       <c r="W44">
-        <v>0.07290000000000001</v>
+        <v>0.1216721085542114</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y44">
-        <v>1.504454653535101</v>
+        <v>0.9008995929222929</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.107695146139338</v>
+        <v>0.108705146139338</v>
       </c>
       <c r="C45">
-        <v>320.9762261264589</v>
+        <v>305.0297833235059</v>
       </c>
       <c r="D45">
-        <v>688.6952261264589</v>
+        <v>682.481783323506</v>
       </c>
       <c r="E45">
-        <v>-40.08100000000002</v>
+        <v>-30.34800000000001</v>
       </c>
       <c r="F45">
-        <v>418.519</v>
+        <v>428.252</v>
       </c>
       <c r="G45">
         <v>50.8</v>
@@ -4977,37 +4977,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M45">
-        <v>61.43858920000001</v>
+        <v>62.86739360000001</v>
       </c>
       <c r="N45">
-        <v>-6.088589200000015</v>
+        <v>-7.517393600000013</v>
       </c>
       <c r="O45">
-        <v>-1.156831948000003</v>
+        <v>-1.428304784000002</v>
       </c>
       <c r="P45">
-        <v>-4.931757252000013</v>
+        <v>-6.08908881600001</v>
       </c>
       <c r="Q45">
-        <v>180.968242748</v>
+        <v>179.810911184</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09715112186145106</v>
+        <v>0.09806810618040555</v>
       </c>
       <c r="T45">
-        <v>0.8658536867153717</v>
+        <v>0.8813153596924319</v>
       </c>
       <c r="U45">
         <v>0.1468</v>
       </c>
       <c r="V45">
-        <v>0.1711709226552356</v>
+        <v>0.1672806744130712</v>
       </c>
       <c r="W45">
-        <v>0.1216721085542114</v>
+        <v>0.1222431969961612</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.9008995929222929</v>
+        <v>0.880424602174059</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.108705146139338</v>
+        <v>0.109715146139338</v>
       </c>
       <c r="C46">
-        <v>305.0297833235059</v>
+        <v>289.1944540328508</v>
       </c>
       <c r="D46">
-        <v>682.481783323506</v>
+        <v>676.3794540328508</v>
       </c>
       <c r="E46">
-        <v>-30.34800000000001</v>
+        <v>-20.61500000000001</v>
       </c>
       <c r="F46">
-        <v>428.252</v>
+        <v>437.985</v>
       </c>
       <c r="G46">
         <v>50.8</v>
@@ -5059,37 +5059,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M46">
-        <v>62.86739360000001</v>
+        <v>64.296198</v>
       </c>
       <c r="N46">
-        <v>-7.517393600000013</v>
+        <v>-8.94619800000001</v>
       </c>
       <c r="O46">
-        <v>-1.428304784000002</v>
+        <v>-1.699777620000002</v>
       </c>
       <c r="P46">
-        <v>-6.08908881600001</v>
+        <v>-7.246420380000008</v>
       </c>
       <c r="Q46">
-        <v>179.810911184</v>
+        <v>178.65357962</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09806810618040555</v>
+        <v>0.09901843538368564</v>
       </c>
       <c r="T46">
-        <v>0.8813153596924319</v>
+        <v>0.8973392753232032</v>
       </c>
       <c r="U46">
         <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.1672806744130712</v>
+        <v>0.1635633260927808</v>
       </c>
       <c r="W46">
-        <v>0.1222431969961612</v>
+        <v>0.1227889037295798</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.880424602174059</v>
+        <v>0.8608596110146356</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.109715146139338</v>
+        <v>0.110725146139338</v>
       </c>
       <c r="C47">
-        <v>289.1944540328508</v>
+        <v>273.4672841437543</v>
       </c>
       <c r="D47">
-        <v>676.3794540328508</v>
+        <v>670.3852841437545</v>
       </c>
       <c r="E47">
-        <v>-20.61500000000001</v>
+        <v>-10.88199999999995</v>
       </c>
       <c r="F47">
-        <v>437.985</v>
+        <v>447.7180000000001</v>
       </c>
       <c r="G47">
         <v>50.8</v>
@@ -5141,37 +5141,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M47">
-        <v>64.296198</v>
+        <v>65.72500240000002</v>
       </c>
       <c r="N47">
-        <v>-8.94619800000001</v>
+        <v>-10.37500240000003</v>
       </c>
       <c r="O47">
-        <v>-1.699777620000002</v>
+        <v>-1.971250456000005</v>
       </c>
       <c r="P47">
-        <v>-7.246420380000008</v>
+        <v>-8.403751944000023</v>
       </c>
       <c r="Q47">
-        <v>178.65357962</v>
+        <v>177.496248056</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09901843538368564</v>
+        <v>0.100003961964865</v>
       </c>
       <c r="T47">
-        <v>0.8973392753232032</v>
+        <v>0.9139566693106701</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1635633260927808</v>
+        <v>0.1600076016125029</v>
       </c>
       <c r="W47">
-        <v>0.1227889037295798</v>
+        <v>0.1233108840832846</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8608596110146356</v>
+        <v>0.8421452716447519</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.110725146139338</v>
+        <v>0.111735146139338</v>
       </c>
       <c r="C48">
-        <v>273.4672841437543</v>
+        <v>257.8454233445753</v>
       </c>
       <c r="D48">
-        <v>670.3852841437545</v>
+        <v>664.4964233445754</v>
       </c>
       <c r="E48">
-        <v>-10.88199999999995</v>
+        <v>-1.148999999999944</v>
       </c>
       <c r="F48">
-        <v>447.7180000000001</v>
+        <v>457.4510000000001</v>
       </c>
       <c r="G48">
         <v>50.8</v>
@@ -5223,37 +5223,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M48">
-        <v>65.72500240000002</v>
+        <v>67.15380680000001</v>
       </c>
       <c r="N48">
-        <v>-10.37500240000003</v>
+        <v>-11.80380680000002</v>
       </c>
       <c r="O48">
-        <v>-1.971250456000005</v>
+        <v>-2.242723292000004</v>
       </c>
       <c r="P48">
-        <v>-8.403751944000023</v>
+        <v>-9.561083508000014</v>
       </c>
       <c r="Q48">
-        <v>177.496248056</v>
+        <v>176.338916492</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.100003961964865</v>
+        <v>0.101026678228353</v>
       </c>
       <c r="T48">
-        <v>0.9139566693106701</v>
+        <v>0.9312011347693621</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.1600076016125029</v>
+        <v>0.1566031845569177</v>
       </c>
       <c r="W48">
-        <v>0.1233108840832846</v>
+        <v>0.1238106525070445</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8421452716447519</v>
+        <v>0.8242272871416723</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.111735146139338</v>
+        <v>0.112745146139338</v>
       </c>
       <c r="C49">
-        <v>257.8454233445753</v>
+        <v>242.3261206034599</v>
       </c>
       <c r="D49">
-        <v>664.4964233445754</v>
+        <v>658.71012060346</v>
       </c>
       <c r="E49">
-        <v>-1.148999999999944</v>
+        <v>8.58400000000006</v>
       </c>
       <c r="F49">
-        <v>457.4510000000001</v>
+        <v>467.1840000000001</v>
       </c>
       <c r="G49">
         <v>50.8</v>
@@ -5305,37 +5305,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M49">
-        <v>67.15380680000001</v>
+        <v>68.58261120000002</v>
       </c>
       <c r="N49">
-        <v>-11.80380680000002</v>
+        <v>-13.23261120000002</v>
       </c>
       <c r="O49">
-        <v>-2.242723292000004</v>
+        <v>-2.514196128000004</v>
       </c>
       <c r="P49">
-        <v>-9.561083508000014</v>
+        <v>-10.71841507200002</v>
       </c>
       <c r="Q49">
-        <v>176.338916492</v>
+        <v>175.181584928</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.101026678228353</v>
+        <v>0.1020887297327444</v>
       </c>
       <c r="T49">
-        <v>0.9312011347693621</v>
+        <v>0.9491088488995421</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1566031845569177</v>
+        <v>0.1533406182119819</v>
       </c>
       <c r="W49">
-        <v>0.1238106525070445</v>
+        <v>0.1242895972464811</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8242272871416723</v>
+        <v>0.8070558853262207</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.112745146139338</v>
+        <v>0.140840543988253</v>
       </c>
       <c r="C50">
-        <v>242.3261206034602</v>
+        <v>104.1485549920483</v>
       </c>
       <c r="D50">
-        <v>658.7101206034603</v>
+        <v>530.2655549920484</v>
       </c>
       <c r="E50">
-        <v>8.584000000000003</v>
+        <v>18.31700000000001</v>
       </c>
       <c r="F50">
-        <v>467.184</v>
+        <v>476.917</v>
       </c>
       <c r="G50">
         <v>50.8</v>
@@ -5387,45 +5387,45 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M50">
-        <v>68.58261120000002</v>
+        <v>95.76493360000001</v>
       </c>
       <c r="N50">
-        <v>-13.23261120000002</v>
+        <v>-40.41493360000001</v>
       </c>
       <c r="O50">
-        <v>-2.514196128000004</v>
+        <v>-7.678837384000002</v>
       </c>
       <c r="P50">
-        <v>-10.71841507200002</v>
+        <v>-32.73609621600001</v>
       </c>
       <c r="Q50">
-        <v>175.181584928</v>
+        <v>153.163903784</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1020887297327444</v>
+        <v>0.1044187006077296</v>
       </c>
       <c r="T50">
-        <v>0.9491088488995421</v>
+        <v>0.9883955051382984</v>
       </c>
       <c r="U50">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1533406182119819</v>
+        <v>0.1098157708115406</v>
       </c>
       <c r="W50">
-        <v>0.1242895972464811</v>
+        <v>0.1787489932210427</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.8070558853262207</v>
+        <v>0.5779777411133713</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.140840543988253</v>
+        <v>0.142390543988253</v>
       </c>
       <c r="C51">
-        <v>104.1485549920483</v>
+        <v>88.77185025211776</v>
       </c>
       <c r="D51">
-        <v>530.2655549920484</v>
+        <v>524.6218502521178</v>
       </c>
       <c r="E51">
-        <v>18.31700000000001</v>
+        <v>28.05000000000001</v>
       </c>
       <c r="F51">
-        <v>476.917</v>
+        <v>486.65</v>
       </c>
       <c r="G51">
         <v>50.8</v>
@@ -5469,37 +5469,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M51">
-        <v>95.76493360000001</v>
+        <v>97.71932000000001</v>
       </c>
       <c r="N51">
-        <v>-40.41493360000001</v>
+        <v>-42.36932000000002</v>
       </c>
       <c r="O51">
-        <v>-7.678837384000002</v>
+        <v>-8.050170800000004</v>
       </c>
       <c r="P51">
-        <v>-32.73609621600001</v>
+        <v>-34.31914920000001</v>
       </c>
       <c r="Q51">
-        <v>153.163903784</v>
+        <v>151.5808508</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1044187006077296</v>
+        <v>0.1055910746198842</v>
       </c>
       <c r="T51">
-        <v>0.9883955051382984</v>
+        <v>1.008163415241065</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1098157708115406</v>
+        <v>0.1076194553953097</v>
       </c>
       <c r="W51">
-        <v>0.1787489932210427</v>
+        <v>0.1791900133566218</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.5779777411133713</v>
+        <v>0.5664181862911039</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.142390543988253</v>
+        <v>0.143940543988253</v>
       </c>
       <c r="C52">
-        <v>88.77185025211776</v>
+        <v>73.51401415501505</v>
       </c>
       <c r="D52">
-        <v>524.6218502521178</v>
+        <v>519.0970141550151</v>
       </c>
       <c r="E52">
-        <v>28.05000000000001</v>
+        <v>37.78300000000002</v>
       </c>
       <c r="F52">
-        <v>486.65</v>
+        <v>496.383</v>
       </c>
       <c r="G52">
         <v>50.8</v>
@@ -5551,37 +5551,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M52">
-        <v>97.71932000000001</v>
+        <v>99.67370640000001</v>
       </c>
       <c r="N52">
-        <v>-42.36932000000002</v>
+        <v>-44.32370640000002</v>
       </c>
       <c r="O52">
-        <v>-8.050170800000004</v>
+        <v>-8.421504216000004</v>
       </c>
       <c r="P52">
-        <v>-34.31914920000001</v>
+        <v>-35.90220218400002</v>
       </c>
       <c r="Q52">
-        <v>151.5808508</v>
+        <v>149.997797816</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1055910746198842</v>
+        <v>0.1068113006325349</v>
       </c>
       <c r="T52">
-        <v>1.008163415241065</v>
+        <v>1.028738178817413</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1076194553953097</v>
+        <v>0.1055092699954017</v>
       </c>
       <c r="W52">
-        <v>0.1791900133566218</v>
+        <v>0.1796137385849234</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.5664181862911039</v>
+        <v>0.5553119473442194</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.143940543988253</v>
+        <v>0.145490543988253</v>
       </c>
       <c r="C53">
-        <v>73.51401415501505</v>
+        <v>58.37133039097699</v>
       </c>
       <c r="D53">
-        <v>519.0970141550151</v>
+        <v>513.6873303909771</v>
       </c>
       <c r="E53">
-        <v>37.78300000000002</v>
+        <v>47.51600000000002</v>
       </c>
       <c r="F53">
-        <v>496.383</v>
+        <v>506.116</v>
       </c>
       <c r="G53">
         <v>50.8</v>
@@ -5633,37 +5633,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M53">
-        <v>99.67370640000001</v>
+        <v>101.6280928</v>
       </c>
       <c r="N53">
-        <v>-44.32370640000002</v>
+        <v>-46.27809280000001</v>
       </c>
       <c r="O53">
-        <v>-8.421504216000004</v>
+        <v>-8.792837632000001</v>
       </c>
       <c r="P53">
-        <v>-35.90220218400002</v>
+        <v>-37.48525516800001</v>
       </c>
       <c r="Q53">
-        <v>149.997797816</v>
+        <v>148.414744832</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1068113006325349</v>
+        <v>0.1080823693957127</v>
       </c>
       <c r="T53">
-        <v>1.028738178817413</v>
+        <v>1.050170224209442</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1055092699954017</v>
+        <v>0.1034802455724132</v>
       </c>
       <c r="W53">
-        <v>0.1796137385849234</v>
+        <v>0.1800211666890594</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5553119473442194</v>
+        <v>0.5446328714337537</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.145490543988253</v>
+        <v>0.147040543988253</v>
       </c>
       <c r="C54">
-        <v>58.37133039097699</v>
+        <v>43.3402359680972</v>
       </c>
       <c r="D54">
-        <v>513.6873303909771</v>
+        <v>508.3892359680972</v>
       </c>
       <c r="E54">
-        <v>47.51600000000002</v>
+        <v>57.24900000000002</v>
       </c>
       <c r="F54">
-        <v>506.116</v>
+        <v>515.849</v>
       </c>
       <c r="G54">
         <v>50.8</v>
@@ -5715,37 +5715,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M54">
-        <v>101.6280928</v>
+        <v>103.5824792</v>
       </c>
       <c r="N54">
-        <v>-46.27809280000001</v>
+        <v>-48.23247920000001</v>
       </c>
       <c r="O54">
-        <v>-8.792837632000001</v>
+        <v>-9.164171048000004</v>
       </c>
       <c r="P54">
-        <v>-37.48525516800001</v>
+        <v>-39.06830815200001</v>
       </c>
       <c r="Q54">
-        <v>148.414744832</v>
+        <v>146.831691848</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1080823693957127</v>
+        <v>0.1094075261913662</v>
       </c>
       <c r="T54">
-        <v>1.050170224209442</v>
+        <v>1.072514271533048</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1034802455724132</v>
+        <v>0.1015277881087828</v>
       </c>
       <c r="W54">
-        <v>0.1800211666890594</v>
+        <v>0.1804132201477564</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5446328714337537</v>
+        <v>0.5343567795199093</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.147040543988253</v>
+        <v>0.148590543988253</v>
       </c>
       <c r="C55">
-        <v>43.3402359680972</v>
+        <v>28.41731338655086</v>
       </c>
       <c r="D55">
-        <v>508.3892359680972</v>
+        <v>503.199313386551</v>
       </c>
       <c r="E55">
-        <v>57.24900000000002</v>
+        <v>66.98200000000008</v>
       </c>
       <c r="F55">
-        <v>515.849</v>
+        <v>525.5820000000001</v>
       </c>
       <c r="G55">
         <v>50.8</v>
@@ -5797,37 +5797,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M55">
-        <v>103.5824792</v>
+        <v>105.5368656</v>
       </c>
       <c r="N55">
-        <v>-48.23247920000001</v>
+        <v>-50.18686560000003</v>
       </c>
       <c r="O55">
-        <v>-9.164171048000004</v>
+        <v>-9.535504464000006</v>
       </c>
       <c r="P55">
-        <v>-39.06830815200001</v>
+        <v>-40.65136113600003</v>
       </c>
       <c r="Q55">
-        <v>146.831691848</v>
+        <v>145.248638864</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1094075261913662</v>
+        <v>0.1107902984998741</v>
       </c>
       <c r="T55">
-        <v>1.072514271533048</v>
+        <v>1.09582979917507</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1015277881087828</v>
+        <v>0.09964764388454603</v>
       </c>
       <c r="W55">
-        <v>0.1804132201477564</v>
+        <v>0.1807907531079831</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5343567795199093</v>
+        <v>0.5244612836028739</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.148590543988253</v>
+        <v>0.150140543988253</v>
       </c>
       <c r="C56">
-        <v>28.41731338655086</v>
+        <v>13.5992832873186</v>
       </c>
       <c r="D56">
-        <v>503.199313386551</v>
+        <v>498.1142832873186</v>
       </c>
       <c r="E56">
-        <v>66.98200000000008</v>
+        <v>76.71500000000003</v>
       </c>
       <c r="F56">
-        <v>525.5820000000001</v>
+        <v>535.3150000000001</v>
       </c>
       <c r="G56">
         <v>50.8</v>
@@ -5879,37 +5879,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M56">
-        <v>105.5368656</v>
+        <v>107.491252</v>
       </c>
       <c r="N56">
-        <v>-50.18686560000003</v>
+        <v>-52.14125200000002</v>
       </c>
       <c r="O56">
-        <v>-9.535504464000006</v>
+        <v>-9.906837880000005</v>
       </c>
       <c r="P56">
-        <v>-40.65136113600003</v>
+        <v>-42.23441412000002</v>
       </c>
       <c r="Q56">
-        <v>145.248638864</v>
+        <v>143.66558588</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1107902984998741</v>
+        <v>0.1122345273554269</v>
       </c>
       <c r="T56">
-        <v>1.09582979917507</v>
+        <v>1.120181572490072</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.09964764388454603</v>
+        <v>0.09783586854119067</v>
       </c>
       <c r="W56">
-        <v>0.1807907531079831</v>
+        <v>0.1811545575969289</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5244612836028739</v>
+        <v>0.5149256239010034</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.150140543988253</v>
+        <v>0.151690543988253</v>
       </c>
       <c r="C57">
-        <v>13.5992832873186</v>
+        <v>-1.117002457827425</v>
       </c>
       <c r="D57">
-        <v>498.1142832873186</v>
+        <v>493.1309975421727</v>
       </c>
       <c r="E57">
-        <v>76.71500000000003</v>
+        <v>86.44800000000009</v>
       </c>
       <c r="F57">
-        <v>535.3150000000001</v>
+        <v>545.0480000000001</v>
       </c>
       <c r="G57">
         <v>50.8</v>
@@ -5961,37 +5961,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M57">
-        <v>107.491252</v>
+        <v>109.4456384</v>
       </c>
       <c r="N57">
-        <v>-52.14125200000002</v>
+        <v>-54.09563840000003</v>
       </c>
       <c r="O57">
-        <v>-9.906837880000005</v>
+        <v>-10.27817129600001</v>
       </c>
       <c r="P57">
-        <v>-42.23441412000002</v>
+        <v>-43.81746710400002</v>
       </c>
       <c r="Q57">
-        <v>143.66558588</v>
+        <v>142.082532896</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1122345273554269</v>
+        <v>0.1137444029771411</v>
       </c>
       <c r="T57">
-        <v>1.120181572490072</v>
+        <v>1.145640244592119</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.09783586854119067</v>
+        <v>0.09608879946009796</v>
       </c>
       <c r="W57">
-        <v>0.1811545575969289</v>
+        <v>0.1815053690684123</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5149256239010034</v>
+        <v>0.5057305234741998</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.151690543988253</v>
+        <v>0.1734428995742585</v>
       </c>
       <c r="C58">
-        <v>-1.117002457827425</v>
+        <v>-71.56097486585941</v>
       </c>
       <c r="D58">
-        <v>493.1309975421727</v>
+        <v>432.4200251341406</v>
       </c>
       <c r="E58">
-        <v>86.44800000000009</v>
+        <v>96.18100000000004</v>
       </c>
       <c r="F58">
-        <v>545.0480000000001</v>
+        <v>554.7810000000001</v>
       </c>
       <c r="G58">
         <v>50.8</v>
@@ -6043,45 +6043,45 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M58">
-        <v>109.4456384</v>
+        <v>130.8173598</v>
       </c>
       <c r="N58">
-        <v>-54.09563840000003</v>
+        <v>-75.46735980000003</v>
       </c>
       <c r="O58">
-        <v>-10.27817129600001</v>
+        <v>-14.33879836200001</v>
       </c>
       <c r="P58">
-        <v>-43.81746710400002</v>
+        <v>-61.12856143800002</v>
       </c>
       <c r="Q58">
-        <v>142.082532896</v>
+        <v>124.771438562</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1137444029771411</v>
+        <v>0.1159113788277851</v>
       </c>
       <c r="T58">
-        <v>1.145640244592119</v>
+        <v>1.182178570558309</v>
       </c>
       <c r="U58">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.09608879946009796</v>
+        <v>0.08039070667744815</v>
       </c>
       <c r="W58">
-        <v>0.1815053690684123</v>
+        <v>0.2168438713654577</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.5057305234741998</v>
+        <v>0.423108982512885</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1734428995742585</v>
+        <v>0.1753428995742585</v>
       </c>
       <c r="C59">
-        <v>-71.56097486585941</v>
+        <v>-85.89455619056866</v>
       </c>
       <c r="D59">
-        <v>432.4200251341406</v>
+        <v>427.8194438094314</v>
       </c>
       <c r="E59">
-        <v>96.18100000000004</v>
+        <v>105.9140000000001</v>
       </c>
       <c r="F59">
-        <v>554.7810000000001</v>
+        <v>564.5140000000001</v>
       </c>
       <c r="G59">
         <v>50.8</v>
@@ -6125,37 +6125,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M59">
-        <v>130.8173598</v>
+        <v>133.1124012</v>
       </c>
       <c r="N59">
-        <v>-75.46735980000003</v>
+        <v>-77.76240120000003</v>
       </c>
       <c r="O59">
-        <v>-14.33879836200001</v>
+        <v>-14.77485622800001</v>
       </c>
       <c r="P59">
-        <v>-61.12856143800002</v>
+        <v>-62.98754497200002</v>
       </c>
       <c r="Q59">
-        <v>124.771438562</v>
+        <v>122.912455028</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1159113788277851</v>
+        <v>0.1175806973713038</v>
       </c>
       <c r="T59">
-        <v>1.182178570558309</v>
+        <v>1.210325679381126</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.08039070667744815</v>
+        <v>0.0790046600105956</v>
       </c>
       <c r="W59">
-        <v>0.2168438713654577</v>
+        <v>0.2171707011695016</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.423108982512885</v>
+        <v>0.4158140000557663</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1753428995742585</v>
+        <v>0.1772428995742585</v>
       </c>
       <c r="C60">
-        <v>-85.89455619056844</v>
+        <v>-100.1312754991052</v>
       </c>
       <c r="D60">
-        <v>427.8194438094316</v>
+        <v>423.3157245008948</v>
       </c>
       <c r="E60">
-        <v>105.914</v>
+        <v>115.6469999999999</v>
       </c>
       <c r="F60">
-        <v>564.514</v>
+        <v>574.247</v>
       </c>
       <c r="G60">
         <v>50.8</v>
@@ -6207,37 +6207,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M60">
-        <v>133.1124012</v>
+        <v>135.4074426</v>
       </c>
       <c r="N60">
-        <v>-77.7624012</v>
+        <v>-80.0574426</v>
       </c>
       <c r="O60">
-        <v>-14.774856228</v>
+        <v>-15.210914094</v>
       </c>
       <c r="P60">
-        <v>-62.98754497199999</v>
+        <v>-64.846528506</v>
       </c>
       <c r="Q60">
-        <v>122.912455028</v>
+        <v>121.053471494</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1175806973713037</v>
+        <v>0.119331446087677</v>
       </c>
       <c r="T60">
-        <v>1.210325679381126</v>
+        <v>1.239845817902617</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07900466001059561</v>
+        <v>0.07766559797651773</v>
       </c>
       <c r="W60">
-        <v>0.2171707011695016</v>
+        <v>0.2174864519971371</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.4158140000557664</v>
+        <v>0.4087663051395669</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1772428995742585</v>
+        <v>0.1791428995742585</v>
       </c>
       <c r="C61">
-        <v>-100.1312754991052</v>
+        <v>-114.2741599667614</v>
       </c>
       <c r="D61">
-        <v>423.3157245008948</v>
+        <v>418.9058400332386</v>
       </c>
       <c r="E61">
-        <v>115.6469999999999</v>
+        <v>125.38</v>
       </c>
       <c r="F61">
-        <v>574.247</v>
+        <v>583.98</v>
       </c>
       <c r="G61">
         <v>50.8</v>
@@ -6289,37 +6289,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M61">
-        <v>135.4074426</v>
+        <v>137.702484</v>
       </c>
       <c r="N61">
-        <v>-80.0574426</v>
+        <v>-82.352484</v>
       </c>
       <c r="O61">
-        <v>-15.210914094</v>
+        <v>-15.64697196</v>
       </c>
       <c r="P61">
-        <v>-64.846528506</v>
+        <v>-66.70551204</v>
       </c>
       <c r="Q61">
-        <v>121.053471494</v>
+        <v>119.19448796</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.119331446087677</v>
+        <v>0.1211697322398689</v>
       </c>
       <c r="T61">
-        <v>1.239845817902617</v>
+        <v>1.270841963350182</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.07766559797651773</v>
+        <v>0.07637117134357575</v>
       </c>
       <c r="W61">
-        <v>0.2174864519971371</v>
+        <v>0.2177916777971849</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4087663051395669</v>
+        <v>0.4019535333872408</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1791428995742585</v>
+        <v>0.1810428995742585</v>
       </c>
       <c r="C62">
-        <v>-114.2741599667614</v>
+        <v>-128.326111927173</v>
       </c>
       <c r="D62">
-        <v>418.9058400332386</v>
+        <v>414.5868880728271</v>
       </c>
       <c r="E62">
-        <v>125.38</v>
+        <v>135.1130000000001</v>
       </c>
       <c r="F62">
-        <v>583.98</v>
+        <v>593.7130000000001</v>
       </c>
       <c r="G62">
         <v>50.8</v>
@@ -6371,37 +6371,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M62">
-        <v>137.702484</v>
+        <v>139.9975254</v>
       </c>
       <c r="N62">
-        <v>-82.352484</v>
+        <v>-84.64752540000003</v>
       </c>
       <c r="O62">
-        <v>-15.64697196</v>
+        <v>-16.08302982600001</v>
       </c>
       <c r="P62">
-        <v>-66.70551204</v>
+        <v>-68.56449557400003</v>
       </c>
       <c r="Q62">
-        <v>119.19448796</v>
+        <v>117.335504426</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1211697322398689</v>
+        <v>0.1231022894767887</v>
       </c>
       <c r="T62">
-        <v>1.270841963350182</v>
+        <v>1.303427654718136</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.07637117134357575</v>
+        <v>0.07511918492810728</v>
       </c>
       <c r="W62">
-        <v>0.2177916777971849</v>
+        <v>0.2180868961939523</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4019535333872408</v>
+        <v>0.3953641312005647</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1810428995742585</v>
+        <v>0.1829428995742585</v>
       </c>
       <c r="C63">
-        <v>-128.326111927173</v>
+        <v>-142.2899152422821</v>
       </c>
       <c r="D63">
-        <v>414.5868880728271</v>
+        <v>410.3560847577179</v>
       </c>
       <c r="E63">
-        <v>135.1130000000001</v>
+        <v>144.846</v>
       </c>
       <c r="F63">
-        <v>593.7130000000001</v>
+        <v>603.446</v>
       </c>
       <c r="G63">
         <v>50.8</v>
@@ -6453,37 +6453,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M63">
-        <v>139.9975254</v>
+        <v>142.2925668</v>
       </c>
       <c r="N63">
-        <v>-84.64752540000003</v>
+        <v>-86.94256680000001</v>
       </c>
       <c r="O63">
-        <v>-16.08302982600001</v>
+        <v>-16.519087692</v>
       </c>
       <c r="P63">
-        <v>-68.56449557400003</v>
+        <v>-70.42347910800001</v>
       </c>
       <c r="Q63">
-        <v>117.335504426</v>
+        <v>115.476520892</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1231022894767887</v>
+        <v>0.1251365602524936</v>
       </c>
       <c r="T63">
-        <v>1.303427654718136</v>
+        <v>1.337728382473876</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.07511918492810728</v>
+        <v>0.07390758517120234</v>
       </c>
       <c r="W63">
-        <v>0.2180868961939523</v>
+        <v>0.2183725914166305</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3953641312005647</v>
+        <v>0.3889872903747492</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1829428995742585</v>
+        <v>0.1848428995742585</v>
       </c>
       <c r="C64">
-        <v>-142.2899152422821</v>
+        <v>-156.16824128621</v>
       </c>
       <c r="D64">
-        <v>410.3560847577179</v>
+        <v>406.21075871379</v>
       </c>
       <c r="E64">
-        <v>144.846</v>
+        <v>154.5790000000001</v>
       </c>
       <c r="F64">
-        <v>603.446</v>
+        <v>613.1790000000001</v>
       </c>
       <c r="G64">
         <v>50.8</v>
@@ -6535,37 +6535,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M64">
-        <v>142.2925668</v>
+        <v>144.5876082</v>
       </c>
       <c r="N64">
-        <v>-86.94256680000001</v>
+        <v>-89.23760820000004</v>
       </c>
       <c r="O64">
-        <v>-16.519087692</v>
+        <v>-16.95514555800001</v>
       </c>
       <c r="P64">
-        <v>-70.42347910800001</v>
+        <v>-72.28246264200003</v>
       </c>
       <c r="Q64">
-        <v>115.476520892</v>
+        <v>113.617537358</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1251365602524936</v>
+        <v>0.1272807916106691</v>
       </c>
       <c r="T64">
-        <v>1.337728382473876</v>
+        <v>1.373883203621818</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.07390758517120234</v>
+        <v>0.07273444889864356</v>
       </c>
       <c r="W64">
-        <v>0.2183725914166305</v>
+        <v>0.2186492169496999</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3889872903747492</v>
+        <v>0.3828128889402292</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1848428995742585</v>
+        <v>0.1867428995742585</v>
       </c>
       <c r="C65">
-        <v>-156.16824128621</v>
+        <v>-169.9636545700716</v>
       </c>
       <c r="D65">
-        <v>406.21075871379</v>
+        <v>402.1483454299284</v>
       </c>
       <c r="E65">
-        <v>154.5790000000001</v>
+        <v>164.312</v>
       </c>
       <c r="F65">
-        <v>613.1790000000001</v>
+        <v>622.912</v>
       </c>
       <c r="G65">
         <v>50.8</v>
@@ -6617,37 +6617,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M65">
-        <v>144.5876082</v>
+        <v>146.8826496</v>
       </c>
       <c r="N65">
-        <v>-89.23760820000004</v>
+        <v>-91.53264960000001</v>
       </c>
       <c r="O65">
-        <v>-16.95514555800001</v>
+        <v>-17.391203424</v>
       </c>
       <c r="P65">
-        <v>-72.28246264200003</v>
+        <v>-74.14144617600002</v>
       </c>
       <c r="Q65">
-        <v>113.617537358</v>
+        <v>111.758553824</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1272807916106691</v>
+        <v>0.1295441469331877</v>
       </c>
       <c r="T65">
-        <v>1.373883203621818</v>
+        <v>1.412046625944647</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.07273444889864356</v>
+        <v>0.07159797313460227</v>
       </c>
       <c r="W65">
-        <v>0.2186492169496999</v>
+        <v>0.2189171979348608</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3828128889402292</v>
+        <v>0.3768314375505383</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1867428995742585</v>
+        <v>0.1886428995742585</v>
       </c>
       <c r="C66">
-        <v>-169.9636545700716</v>
+        <v>-183.6786180326177</v>
       </c>
       <c r="D66">
-        <v>402.1483454299284</v>
+        <v>398.1663819673824</v>
       </c>
       <c r="E66">
-        <v>164.312</v>
+        <v>174.0450000000001</v>
       </c>
       <c r="F66">
-        <v>622.912</v>
+        <v>632.6450000000001</v>
       </c>
       <c r="G66">
         <v>50.8</v>
@@ -6699,37 +6699,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M66">
-        <v>146.8826496</v>
+        <v>149.177691</v>
       </c>
       <c r="N66">
-        <v>-91.53264960000001</v>
+        <v>-93.82769100000004</v>
       </c>
       <c r="O66">
-        <v>-17.391203424</v>
+        <v>-17.82726129000001</v>
       </c>
       <c r="P66">
-        <v>-74.14144617600002</v>
+        <v>-76.00042971000003</v>
       </c>
       <c r="Q66">
-        <v>111.758553824</v>
+        <v>109.89957029</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1295441469331877</v>
+        <v>0.1319368368455645</v>
       </c>
       <c r="T66">
-        <v>1.412046625944647</v>
+        <v>1.452390815257351</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07159797313460227</v>
+        <v>0.07049646585560837</v>
       </c>
       <c r="W66">
-        <v>0.2189171979348608</v>
+        <v>0.2191769333512475</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3768314375505383</v>
+        <v>0.3710340308189914</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1886428995742585</v>
+        <v>0.1905428995742585</v>
       </c>
       <c r="C67">
-        <v>-183.6786180326177</v>
+        <v>-197.3154980196393</v>
       </c>
       <c r="D67">
-        <v>398.1663819673824</v>
+        <v>394.2625019803608</v>
       </c>
       <c r="E67">
-        <v>174.0450000000001</v>
+        <v>183.778</v>
       </c>
       <c r="F67">
-        <v>632.6450000000001</v>
+        <v>642.378</v>
       </c>
       <c r="G67">
         <v>50.8</v>
@@ -6781,37 +6781,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M67">
-        <v>149.177691</v>
+        <v>151.4727324</v>
       </c>
       <c r="N67">
-        <v>-93.82769100000004</v>
+        <v>-96.12273240000002</v>
       </c>
       <c r="O67">
-        <v>-17.82726129000001</v>
+        <v>-18.263319156</v>
       </c>
       <c r="P67">
-        <v>-76.00042971000003</v>
+        <v>-77.85941324400001</v>
       </c>
       <c r="Q67">
-        <v>109.89957029</v>
+        <v>108.040586756</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1319368368455645</v>
+        <v>0.1344702732233752</v>
       </c>
       <c r="T67">
-        <v>1.452390815257351</v>
+        <v>1.495108192176685</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07049646585560837</v>
+        <v>0.06942833758506887</v>
       </c>
       <c r="W67">
-        <v>0.2191769333512475</v>
+        <v>0.2194287979974408</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3710340308189914</v>
+        <v>0.3654123030793098</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1905428995742585</v>
+        <v>0.1924428995742585</v>
       </c>
       <c r="C68">
-        <v>-197.3154980196393</v>
+        <v>-210.8765689732896</v>
       </c>
       <c r="D68">
-        <v>394.2625019803608</v>
+        <v>390.4344310267105</v>
       </c>
       <c r="E68">
-        <v>183.778</v>
+        <v>193.5110000000001</v>
       </c>
       <c r="F68">
-        <v>642.378</v>
+        <v>652.1110000000001</v>
       </c>
       <c r="G68">
         <v>50.8</v>
@@ -6863,37 +6863,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M68">
-        <v>151.4727324</v>
+        <v>153.7677738</v>
       </c>
       <c r="N68">
-        <v>-96.12273240000002</v>
+        <v>-98.41777380000005</v>
       </c>
       <c r="O68">
-        <v>-18.263319156</v>
+        <v>-18.69937702200001</v>
       </c>
       <c r="P68">
-        <v>-77.85941324400001</v>
+        <v>-79.71839677800004</v>
       </c>
       <c r="Q68">
-        <v>108.040586756</v>
+        <v>106.181603222</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1344702732233752</v>
+        <v>0.1371572511998412</v>
       </c>
       <c r="T68">
-        <v>1.495108192176685</v>
+        <v>1.540414501030524</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06942833758506887</v>
+        <v>0.06839209374051558</v>
       </c>
       <c r="W68">
-        <v>0.2194287979974408</v>
+        <v>0.2196731442959864</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3654123030793098</v>
+        <v>0.3599583881079768</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1924428995742585</v>
+        <v>0.1943428995742585</v>
       </c>
       <c r="C69">
-        <v>-210.8765689732896</v>
+        <v>-224.3640178508471</v>
       </c>
       <c r="D69">
-        <v>390.4344310267105</v>
+        <v>386.679982149153</v>
       </c>
       <c r="E69">
-        <v>193.5110000000001</v>
+        <v>203.244</v>
       </c>
       <c r="F69">
-        <v>652.1110000000001</v>
+        <v>661.8440000000001</v>
       </c>
       <c r="G69">
         <v>50.8</v>
@@ -6945,37 +6945,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M69">
-        <v>153.7677738</v>
+        <v>156.0628152</v>
       </c>
       <c r="N69">
-        <v>-98.41777380000005</v>
+        <v>-100.7128152</v>
       </c>
       <c r="O69">
-        <v>-18.69937702200001</v>
+        <v>-19.13543488800001</v>
       </c>
       <c r="P69">
-        <v>-79.71839677800004</v>
+        <v>-81.57738031200002</v>
       </c>
       <c r="Q69">
-        <v>106.181603222</v>
+        <v>104.322619688</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1371572511998412</v>
+        <v>0.1400121652998362</v>
       </c>
       <c r="T69">
-        <v>1.540414501030524</v>
+        <v>1.588552454187728</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06839209374051558</v>
+        <v>0.06738632765609626</v>
       </c>
       <c r="W69">
-        <v>0.2196731442959864</v>
+        <v>0.2199103039386925</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3599583881079768</v>
+        <v>0.3546648824005065</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1943428995742585</v>
+        <v>0.1962428995742585</v>
       </c>
       <c r="C70">
-        <v>-224.3640178508471</v>
+        <v>-237.7799482909611</v>
       </c>
       <c r="D70">
-        <v>386.679982149153</v>
+        <v>382.997051709039</v>
       </c>
       <c r="E70">
-        <v>203.244</v>
+        <v>212.9770000000001</v>
       </c>
       <c r="F70">
-        <v>661.8440000000001</v>
+        <v>671.5770000000001</v>
       </c>
       <c r="G70">
         <v>50.8</v>
@@ -7027,37 +7027,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M70">
-        <v>156.0628152</v>
+        <v>158.3578566</v>
       </c>
       <c r="N70">
-        <v>-100.7128152</v>
+        <v>-103.0078566</v>
       </c>
       <c r="O70">
-        <v>-19.13543488800001</v>
+        <v>-19.571492754</v>
       </c>
       <c r="P70">
-        <v>-81.57738031200002</v>
+        <v>-83.43636384600002</v>
       </c>
       <c r="Q70">
-        <v>104.322619688</v>
+        <v>102.463636154</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1400121652998362</v>
+        <v>0.1430512674062825</v>
       </c>
       <c r="T70">
-        <v>1.588552454187728</v>
+        <v>1.639796081742171</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06738632765609626</v>
+        <v>0.066409714211805</v>
       </c>
       <c r="W70">
-        <v>0.2199103039386925</v>
+        <v>0.2201405893888564</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3546648824005065</v>
+        <v>0.349524811641079</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1962428995742585</v>
+        <v>0.1981428995742585</v>
       </c>
       <c r="C71">
-        <v>-237.7799482909611</v>
+        <v>-251.1263845440542</v>
       </c>
       <c r="D71">
-        <v>382.997051709039</v>
+        <v>379.3836154559459</v>
       </c>
       <c r="E71">
-        <v>212.9770000000001</v>
+        <v>222.71</v>
       </c>
       <c r="F71">
-        <v>671.5770000000001</v>
+        <v>681.3100000000001</v>
       </c>
       <c r="G71">
         <v>50.8</v>
@@ -7109,37 +7109,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M71">
-        <v>158.3578566</v>
+        <v>160.652898</v>
       </c>
       <c r="N71">
-        <v>-103.0078566</v>
+        <v>-105.302898</v>
       </c>
       <c r="O71">
-        <v>-19.571492754</v>
+        <v>-20.00755062000001</v>
       </c>
       <c r="P71">
-        <v>-83.43636384600002</v>
+        <v>-85.29534738000002</v>
       </c>
       <c r="Q71">
-        <v>102.463636154</v>
+        <v>100.60465262</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1430512674062825</v>
+        <v>0.1462929763198253</v>
       </c>
       <c r="T71">
-        <v>1.639796081742171</v>
+        <v>1.694455951133577</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.066409714211805</v>
+        <v>0.06546100400877922</v>
       </c>
       <c r="W71">
-        <v>0.2201405893888564</v>
+        <v>0.2203642952547299</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.349524811641079</v>
+        <v>0.3445316000462064</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1981428995742585</v>
+        <v>0.2000428995742585</v>
       </c>
       <c r="C72">
-        <v>-251.1263845440542</v>
+        <v>-264.4052751823144</v>
       </c>
       <c r="D72">
-        <v>379.3836154559459</v>
+        <v>375.8377248176857</v>
       </c>
       <c r="E72">
-        <v>222.71</v>
+        <v>232.4430000000001</v>
       </c>
       <c r="F72">
-        <v>681.3100000000001</v>
+        <v>691.0430000000001</v>
       </c>
       <c r="G72">
         <v>50.8</v>
@@ -7191,37 +7191,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M72">
-        <v>160.652898</v>
+        <v>162.9479394</v>
       </c>
       <c r="N72">
-        <v>-105.302898</v>
+        <v>-107.5979394</v>
       </c>
       <c r="O72">
-        <v>-20.00755062000001</v>
+        <v>-20.44360848600001</v>
       </c>
       <c r="P72">
-        <v>-85.29534738000002</v>
+        <v>-87.15433091400003</v>
       </c>
       <c r="Q72">
-        <v>100.60465262</v>
+        <v>98.74566908599998</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1462929763198253</v>
+        <v>0.1497582513653365</v>
       </c>
       <c r="T72">
-        <v>1.694455951133577</v>
+        <v>1.752885466689907</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06546100400877922</v>
+        <v>0.06453901803682457</v>
       </c>
       <c r="W72">
-        <v>0.2203642952547299</v>
+        <v>0.2205816995469168</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3445316000462064</v>
+        <v>0.3396790422990767</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2000428995742585</v>
+        <v>0.2019428995742585</v>
       </c>
       <c r="C73">
-        <v>-264.4052751823143</v>
+        <v>-277.6184966035598</v>
       </c>
       <c r="D73">
-        <v>375.8377248176857</v>
+        <v>372.3575033964403</v>
       </c>
       <c r="E73">
-        <v>232.443</v>
+        <v>242.176</v>
       </c>
       <c r="F73">
-        <v>691.043</v>
+        <v>700.7760000000001</v>
       </c>
       <c r="G73">
         <v>50.8</v>
@@ -7273,37 +7273,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M73">
-        <v>162.9479394</v>
+        <v>165.2429808</v>
       </c>
       <c r="N73">
-        <v>-107.5979394</v>
+        <v>-109.8929808</v>
       </c>
       <c r="O73">
-        <v>-20.443608486</v>
+        <v>-20.87966635200001</v>
       </c>
       <c r="P73">
-        <v>-87.154330914</v>
+        <v>-89.01331444800002</v>
       </c>
       <c r="Q73">
-        <v>98.74566908600001</v>
+        <v>96.88668555199999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1497582513653365</v>
+        <v>0.1534710460569556</v>
       </c>
       <c r="T73">
-        <v>1.752885466689906</v>
+        <v>1.815488519071689</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06453901803682459</v>
+        <v>0.06364264278631312</v>
       </c>
       <c r="W73">
-        <v>0.2205816995469168</v>
+        <v>0.2207930648309874</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3396790422990767</v>
+        <v>0.3349612778227006</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2019428995742585</v>
+        <v>0.2038428995742585</v>
       </c>
       <c r="C74">
-        <v>-277.6184966035598</v>
+        <v>-290.7678563422194</v>
       </c>
       <c r="D74">
-        <v>372.3575033964403</v>
+        <v>368.9411436577806</v>
       </c>
       <c r="E74">
-        <v>242.176</v>
+        <v>251.909</v>
       </c>
       <c r="F74">
-        <v>700.7760000000001</v>
+        <v>710.509</v>
       </c>
       <c r="G74">
         <v>50.8</v>
@@ -7355,37 +7355,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M74">
-        <v>165.2429808</v>
+        <v>167.5380222</v>
       </c>
       <c r="N74">
-        <v>-109.8929808</v>
+        <v>-112.1880222</v>
       </c>
       <c r="O74">
-        <v>-20.87966635200001</v>
+        <v>-21.315724218</v>
       </c>
       <c r="P74">
-        <v>-89.01331444800002</v>
+        <v>-90.87229798200001</v>
       </c>
       <c r="Q74">
-        <v>96.88668555199999</v>
+        <v>95.027702018</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1534710460569556</v>
+        <v>0.1574588625775836</v>
       </c>
       <c r="T74">
-        <v>1.815488519071689</v>
+        <v>1.882728834592862</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06364264278631312</v>
+        <v>0.06277082576184308</v>
       </c>
       <c r="W74">
-        <v>0.2207930648309874</v>
+        <v>0.2209986392853574</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3349612778227006</v>
+        <v>0.3303727671675952</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2038428995742585</v>
+        <v>0.2057428995742585</v>
       </c>
       <c r="C75">
-        <v>-290.7678563422194</v>
+        <v>-303.8550961997009</v>
       </c>
       <c r="D75">
-        <v>368.9411436577806</v>
+        <v>365.5869038002991</v>
       </c>
       <c r="E75">
-        <v>251.909</v>
+        <v>261.6420000000001</v>
       </c>
       <c r="F75">
-        <v>710.509</v>
+        <v>720.2420000000001</v>
       </c>
       <c r="G75">
         <v>50.8</v>
@@ -7437,37 +7437,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M75">
-        <v>167.5380222</v>
+        <v>169.8330636</v>
       </c>
       <c r="N75">
-        <v>-112.1880222</v>
+        <v>-114.4830636</v>
       </c>
       <c r="O75">
-        <v>-21.315724218</v>
+        <v>-21.75178208400001</v>
       </c>
       <c r="P75">
-        <v>-90.87229798200001</v>
+        <v>-92.73128151600002</v>
       </c>
       <c r="Q75">
-        <v>95.027702018</v>
+        <v>93.16871848399998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1574588625775836</v>
+        <v>0.161753434215183</v>
       </c>
       <c r="T75">
-        <v>1.882728834592862</v>
+        <v>1.955141482077203</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06277082576184308</v>
+        <v>0.061922571359656</v>
       </c>
       <c r="W75">
-        <v>0.2209986392853574</v>
+        <v>0.2211986576733931</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3303727671675952</v>
+        <v>0.325908270313979</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2057428995742585</v>
+        <v>0.2076428995742585</v>
       </c>
       <c r="C76">
-        <v>-303.8550961997009</v>
+        <v>-316.8818952055375</v>
       </c>
       <c r="D76">
-        <v>365.5869038002991</v>
+        <v>362.2931047944625</v>
       </c>
       <c r="E76">
-        <v>261.6420000000001</v>
+        <v>271.375</v>
       </c>
       <c r="F76">
-        <v>720.2420000000001</v>
+        <v>729.975</v>
       </c>
       <c r="G76">
         <v>50.8</v>
@@ -7519,37 +7519,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M76">
-        <v>169.8330636</v>
+        <v>172.128105</v>
       </c>
       <c r="N76">
-        <v>-114.4830636</v>
+        <v>-116.778105</v>
       </c>
       <c r="O76">
-        <v>-21.75178208400001</v>
+        <v>-22.18783995</v>
       </c>
       <c r="P76">
-        <v>-92.73128151600002</v>
+        <v>-94.59026505000001</v>
       </c>
       <c r="Q76">
-        <v>93.16871848399998</v>
+        <v>91.30973494999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.161753434215183</v>
+        <v>0.1663915715837903</v>
       </c>
       <c r="T76">
-        <v>1.955141482077203</v>
+        <v>2.033347141360291</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.061922571359656</v>
+        <v>0.0610969370748606</v>
       </c>
       <c r="W76">
-        <v>0.2211986576733931</v>
+        <v>0.2213933422377479</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.325908270313979</v>
+        <v>0.3215628267097926</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2076428995742585</v>
+        <v>0.2095428995742585</v>
       </c>
       <c r="C77">
-        <v>-316.8818952055375</v>
+        <v>-329.8498724198938</v>
       </c>
       <c r="D77">
-        <v>362.2931047944625</v>
+        <v>359.0581275801063</v>
       </c>
       <c r="E77">
-        <v>271.375</v>
+        <v>281.1080000000001</v>
       </c>
       <c r="F77">
-        <v>729.975</v>
+        <v>739.7080000000001</v>
       </c>
       <c r="G77">
         <v>50.8</v>
@@ -7601,37 +7601,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M77">
-        <v>172.128105</v>
+        <v>174.4231464</v>
       </c>
       <c r="N77">
-        <v>-116.778105</v>
+        <v>-119.0731464</v>
       </c>
       <c r="O77">
-        <v>-22.18783995</v>
+        <v>-22.62389781600001</v>
       </c>
       <c r="P77">
-        <v>-94.59026505000001</v>
+        <v>-96.44924858400003</v>
       </c>
       <c r="Q77">
-        <v>91.30973494999999</v>
+        <v>89.45075141599997</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1663915715837903</v>
+        <v>0.1714162203997816</v>
       </c>
       <c r="T77">
-        <v>2.033347141360291</v>
+        <v>2.118069938916971</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0610969370748606</v>
+        <v>0.06029303000808611</v>
       </c>
       <c r="W77">
-        <v>0.2213933422377479</v>
+        <v>0.2215829035240933</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3215628267097926</v>
+        <v>0.3173317368846638</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2095428995742585</v>
+        <v>0.2114428995742585</v>
       </c>
       <c r="C78">
-        <v>-329.8498724198938</v>
+        <v>-342.7605895872521</v>
       </c>
       <c r="D78">
-        <v>359.0581275801063</v>
+        <v>355.8804104127479</v>
       </c>
       <c r="E78">
-        <v>281.1080000000001</v>
+        <v>290.841</v>
       </c>
       <c r="F78">
-        <v>739.7080000000001</v>
+        <v>749.441</v>
       </c>
       <c r="G78">
         <v>50.8</v>
@@ -7683,37 +7683,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M78">
-        <v>174.4231464</v>
+        <v>176.7181878</v>
       </c>
       <c r="N78">
-        <v>-119.0731464</v>
+        <v>-121.3681878</v>
       </c>
       <c r="O78">
-        <v>-22.62389781600001</v>
+        <v>-23.059955682</v>
       </c>
       <c r="P78">
-        <v>-96.44924858400003</v>
+        <v>-98.30823211800001</v>
       </c>
       <c r="Q78">
-        <v>89.45075141599997</v>
+        <v>87.591767882</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1714162203997816</v>
+        <v>0.1768777951997721</v>
       </c>
       <c r="T78">
-        <v>2.118069938916971</v>
+        <v>2.210159936261186</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06029303000808611</v>
+        <v>0.05951000364434474</v>
       </c>
       <c r="W78">
-        <v>0.2215829035240933</v>
+        <v>0.2217675411406635</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3173317368846638</v>
+        <v>0.3132105454965513</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2114428995742585</v>
+        <v>0.2133428995742585</v>
       </c>
       <c r="C79">
-        <v>-342.7605895872521</v>
+        <v>-355.6155536504264</v>
       </c>
       <c r="D79">
-        <v>355.8804104127479</v>
+        <v>352.7584463495737</v>
       </c>
       <c r="E79">
-        <v>290.841</v>
+        <v>300.5740000000001</v>
       </c>
       <c r="F79">
-        <v>749.441</v>
+        <v>759.1740000000001</v>
       </c>
       <c r="G79">
         <v>50.8</v>
@@ -7765,37 +7765,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M79">
-        <v>176.7181878</v>
+        <v>179.0132292</v>
       </c>
       <c r="N79">
-        <v>-121.3681878</v>
+        <v>-123.6632292</v>
       </c>
       <c r="O79">
-        <v>-23.059955682</v>
+        <v>-23.49601354800001</v>
       </c>
       <c r="P79">
-        <v>-98.30823211800001</v>
+        <v>-100.167215652</v>
       </c>
       <c r="Q79">
-        <v>87.591767882</v>
+        <v>85.73278434799997</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1768777951997721</v>
+        <v>0.1828358767997617</v>
       </c>
       <c r="T79">
-        <v>2.210159936261186</v>
+        <v>2.310621751545786</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05951000364434474</v>
+        <v>0.05874705487967364</v>
       </c>
       <c r="W79">
-        <v>0.2217675411406635</v>
+        <v>0.221947444459373</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3132105454965513</v>
+        <v>0.3091950256824929</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2133428995742585</v>
+        <v>0.2152428995742585</v>
       </c>
       <c r="C80">
-        <v>-355.6155536504264</v>
+        <v>-368.4162191333977</v>
       </c>
       <c r="D80">
-        <v>352.7584463495737</v>
+        <v>349.6907808666023</v>
       </c>
       <c r="E80">
-        <v>300.5740000000001</v>
+        <v>310.307</v>
       </c>
       <c r="F80">
-        <v>759.1740000000001</v>
+        <v>768.907</v>
       </c>
       <c r="G80">
         <v>50.8</v>
@@ -7847,37 +7847,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M80">
-        <v>179.0132292</v>
+        <v>181.3082706</v>
       </c>
       <c r="N80">
-        <v>-123.6632292</v>
+        <v>-125.9582706</v>
       </c>
       <c r="O80">
-        <v>-23.49601354800001</v>
+        <v>-23.932071414</v>
       </c>
       <c r="P80">
-        <v>-100.167215652</v>
+        <v>-102.026199186</v>
       </c>
       <c r="Q80">
-        <v>85.73278434799997</v>
+        <v>83.87380081399999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1828358767997617</v>
+        <v>0.1893613947426075</v>
       </c>
       <c r="T80">
-        <v>2.310621751545786</v>
+        <v>2.420651358762252</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05874705487967364</v>
+        <v>0.05800342127360184</v>
       </c>
       <c r="W80">
-        <v>0.221947444459373</v>
+        <v>0.2221227932636847</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3091950256824929</v>
+        <v>0.3052811645979044</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2152428995742585</v>
+        <v>0.2171428995742585</v>
       </c>
       <c r="C81">
-        <v>-368.4162191333977</v>
+        <v>-381.1639904008942</v>
       </c>
       <c r="D81">
-        <v>349.6907808666023</v>
+        <v>346.6760095991058</v>
       </c>
       <c r="E81">
-        <v>310.307</v>
+        <v>320.0400000000001</v>
       </c>
       <c r="F81">
-        <v>768.907</v>
+        <v>778.6400000000001</v>
       </c>
       <c r="G81">
         <v>50.8</v>
@@ -7929,37 +7929,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M81">
-        <v>181.3082706</v>
+        <v>183.603312</v>
       </c>
       <c r="N81">
-        <v>-125.9582706</v>
+        <v>-128.2533120000001</v>
       </c>
       <c r="O81">
-        <v>-23.932071414</v>
+        <v>-24.36812928000001</v>
       </c>
       <c r="P81">
-        <v>-102.026199186</v>
+        <v>-103.88518272</v>
       </c>
       <c r="Q81">
-        <v>83.87380081399999</v>
+        <v>82.01481727999996</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1893613947426075</v>
+        <v>0.1965394644797379</v>
       </c>
       <c r="T81">
-        <v>2.420651358762252</v>
+        <v>2.541683926700365</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05800342127360184</v>
+        <v>0.0572783785076818</v>
       </c>
       <c r="W81">
-        <v>0.2221227932636847</v>
+        <v>0.2222937583478886</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3052811645979044</v>
+        <v>0.3014651500404305</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2171428995742585</v>
+        <v>0.2190428995742585</v>
       </c>
       <c r="C82">
-        <v>-381.1639904008942</v>
+        <v>-393.8602238020866</v>
       </c>
       <c r="D82">
-        <v>346.6760095991058</v>
+        <v>343.7127761979135</v>
       </c>
       <c r="E82">
-        <v>320.0400000000001</v>
+        <v>329.7730000000001</v>
       </c>
       <c r="F82">
-        <v>778.6400000000001</v>
+        <v>788.3730000000002</v>
       </c>
       <c r="G82">
         <v>50.8</v>
@@ -8011,37 +8011,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M82">
-        <v>183.603312</v>
+        <v>185.8983534</v>
       </c>
       <c r="N82">
-        <v>-128.2533120000001</v>
+        <v>-130.5483534000001</v>
       </c>
       <c r="O82">
-        <v>-24.36812928000001</v>
+        <v>-24.80418714600001</v>
       </c>
       <c r="P82">
-        <v>-103.88518272</v>
+        <v>-105.744166254</v>
       </c>
       <c r="Q82">
-        <v>82.01481727999996</v>
+        <v>80.15583374599996</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1965394644797379</v>
+        <v>0.2044731205049873</v>
       </c>
       <c r="T82">
-        <v>2.541683926700365</v>
+        <v>2.675456764947753</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0572783785076818</v>
+        <v>0.05657123803227833</v>
       </c>
       <c r="W82">
-        <v>0.2222937583478886</v>
+        <v>0.2224605020719888</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3014651500404305</v>
+        <v>0.2977433580646227</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2190428995742585</v>
+        <v>0.2209428995742585</v>
       </c>
       <c r="C83">
-        <v>-393.8602238020866</v>
+        <v>-406.506229705275</v>
       </c>
       <c r="D83">
-        <v>343.7127761979135</v>
+        <v>340.7997702947251</v>
       </c>
       <c r="E83">
-        <v>329.7730000000001</v>
+        <v>339.5060000000001</v>
       </c>
       <c r="F83">
-        <v>788.3730000000002</v>
+        <v>798.1060000000001</v>
       </c>
       <c r="G83">
         <v>50.8</v>
@@ -8093,37 +8093,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M83">
-        <v>185.8983534</v>
+        <v>188.1933948</v>
       </c>
       <c r="N83">
-        <v>-130.5483534000001</v>
+        <v>-132.8433948</v>
       </c>
       <c r="O83">
-        <v>-24.80418714600001</v>
+        <v>-25.24024501200001</v>
       </c>
       <c r="P83">
-        <v>-105.744166254</v>
+        <v>-107.603149788</v>
       </c>
       <c r="Q83">
-        <v>80.15583374599996</v>
+        <v>78.29685021199998</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2044731205049873</v>
+        <v>0.2132882938663755</v>
       </c>
       <c r="T83">
-        <v>2.675456764947753</v>
+        <v>2.824093251889295</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05657123803227833</v>
+        <v>0.05588134488554323</v>
       </c>
       <c r="W83">
-        <v>0.2224605020719888</v>
+        <v>0.2226231788759889</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2977433580646227</v>
+        <v>0.2941123415028591</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2209428995742585</v>
+        <v>0.2228428995742585</v>
       </c>
       <c r="C84">
-        <v>-406.506229705275</v>
+        <v>-419.1032744299812</v>
       </c>
       <c r="D84">
-        <v>340.7997702947251</v>
+        <v>337.935725570019</v>
       </c>
       <c r="E84">
-        <v>339.5060000000001</v>
+        <v>349.2390000000001</v>
       </c>
       <c r="F84">
-        <v>798.1060000000001</v>
+        <v>807.8390000000002</v>
       </c>
       <c r="G84">
         <v>50.8</v>
@@ -8175,37 +8175,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M84">
-        <v>188.1933948</v>
+        <v>190.4884362000001</v>
       </c>
       <c r="N84">
-        <v>-132.8433948</v>
+        <v>-135.1384362000001</v>
       </c>
       <c r="O84">
-        <v>-25.24024501200001</v>
+        <v>-25.67630287800001</v>
       </c>
       <c r="P84">
-        <v>-107.603149788</v>
+        <v>-109.462133322</v>
       </c>
       <c r="Q84">
-        <v>78.29685021199998</v>
+        <v>76.43786667799996</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2132882938663755</v>
+        <v>0.2231405464467505</v>
       </c>
       <c r="T84">
-        <v>2.824093251889295</v>
+        <v>2.990216384353371</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05588134488554323</v>
+        <v>0.05520807567005475</v>
       </c>
       <c r="W84">
-        <v>0.2226231788759889</v>
+        <v>0.2227819357570011</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2941123415028591</v>
+        <v>0.2905688193160776</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2228428995742585</v>
+        <v>0.2247428995742585</v>
       </c>
       <c r="C85">
-        <v>-419.1032744299812</v>
+        <v>-431.6525820824286</v>
       </c>
       <c r="D85">
-        <v>337.935725570019</v>
+        <v>335.1194179175715</v>
       </c>
       <c r="E85">
-        <v>349.2390000000001</v>
+        <v>358.9720000000001</v>
       </c>
       <c r="F85">
-        <v>807.8390000000002</v>
+        <v>817.5720000000001</v>
       </c>
       <c r="G85">
         <v>50.8</v>
@@ -8257,37 +8257,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M85">
-        <v>190.4884362000001</v>
+        <v>192.7834776</v>
       </c>
       <c r="N85">
-        <v>-135.1384362000001</v>
+        <v>-137.4334776</v>
       </c>
       <c r="O85">
-        <v>-25.67630287800001</v>
+        <v>-26.11236074400001</v>
       </c>
       <c r="P85">
-        <v>-109.462133322</v>
+        <v>-111.321116856</v>
       </c>
       <c r="Q85">
-        <v>76.43786667799996</v>
+        <v>74.57888314399997</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2231405464467505</v>
+        <v>0.2342243305996725</v>
       </c>
       <c r="T85">
-        <v>2.990216384353371</v>
+        <v>3.177104908375457</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05520807567005475</v>
+        <v>0.05455083667398267</v>
       </c>
       <c r="W85">
-        <v>0.2227819357570011</v>
+        <v>0.2229369127122749</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2905688193160776</v>
+        <v>0.287109666705172</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2247428995742585</v>
+        <v>0.2266428995742585</v>
       </c>
       <c r="C86">
-        <v>-431.6525820824284</v>
+        <v>-444.1553363000031</v>
       </c>
       <c r="D86">
-        <v>335.1194179175716</v>
+        <v>332.3496636999969</v>
       </c>
       <c r="E86">
-        <v>358.972</v>
+        <v>368.705</v>
       </c>
       <c r="F86">
-        <v>817.572</v>
+        <v>827.3050000000001</v>
       </c>
       <c r="G86">
         <v>50.8</v>
@@ -8339,37 +8339,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M86">
-        <v>192.7834776</v>
+        <v>195.078519</v>
       </c>
       <c r="N86">
-        <v>-137.4334776</v>
+        <v>-139.728519</v>
       </c>
       <c r="O86">
-        <v>-26.112360744</v>
+        <v>-26.54841861000001</v>
       </c>
       <c r="P86">
-        <v>-111.321116856</v>
+        <v>-113.18010039</v>
       </c>
       <c r="Q86">
-        <v>74.578883144</v>
+        <v>72.71989960999997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2342243305996723</v>
+        <v>0.2467859526396505</v>
       </c>
       <c r="T86">
-        <v>3.177104908375455</v>
+        <v>3.388911902267152</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05455083667398268</v>
+        <v>0.053909062124877</v>
       </c>
       <c r="W86">
-        <v>0.2229369127122749</v>
+        <v>0.223088243150954</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.287109666705172</v>
+        <v>0.2837319059204052</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2266428995742585</v>
+        <v>0.2285428995742585</v>
       </c>
       <c r="C87">
-        <v>-444.1553363000031</v>
+        <v>-456.6126819099131</v>
       </c>
       <c r="D87">
-        <v>332.3496636999969</v>
+        <v>329.6253180900869</v>
       </c>
       <c r="E87">
-        <v>368.705</v>
+        <v>378.438</v>
       </c>
       <c r="F87">
-        <v>827.3050000000001</v>
+        <v>837.038</v>
       </c>
       <c r="G87">
         <v>50.8</v>
@@ -8421,37 +8421,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M87">
-        <v>195.078519</v>
+        <v>197.3735604</v>
       </c>
       <c r="N87">
-        <v>-139.728519</v>
+        <v>-142.0235604</v>
       </c>
       <c r="O87">
-        <v>-26.54841861000001</v>
+        <v>-26.984476476</v>
       </c>
       <c r="P87">
-        <v>-113.18010039</v>
+        <v>-115.039083924</v>
       </c>
       <c r="Q87">
-        <v>72.71989960999997</v>
+        <v>70.860916076</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2467859526396505</v>
+        <v>0.2611420921139113</v>
       </c>
       <c r="T87">
-        <v>3.388911902267152</v>
+        <v>3.630977038143377</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.053909062124877</v>
+        <v>0.05328221256528542</v>
       </c>
       <c r="W87">
-        <v>0.223088243150954</v>
+        <v>0.2232360542771057</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2837319059204052</v>
+        <v>0.2804326977120285</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2285428995742585</v>
+        <v>0.2304428995742585</v>
       </c>
       <c r="C88">
-        <v>-456.6126819099131</v>
+        <v>-469.0257265069365</v>
       </c>
       <c r="D88">
-        <v>329.6253180900869</v>
+        <v>326.9452734930636</v>
       </c>
       <c r="E88">
-        <v>378.438</v>
+        <v>388.171</v>
       </c>
       <c r="F88">
-        <v>837.038</v>
+        <v>846.7710000000001</v>
       </c>
       <c r="G88">
         <v>50.8</v>
@@ -8503,37 +8503,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M88">
-        <v>197.3735604</v>
+        <v>199.6686018</v>
       </c>
       <c r="N88">
-        <v>-142.0235604</v>
+        <v>-144.3186018</v>
       </c>
       <c r="O88">
-        <v>-26.984476476</v>
+        <v>-27.42053434200001</v>
       </c>
       <c r="P88">
-        <v>-115.039083924</v>
+        <v>-116.898067458</v>
       </c>
       <c r="Q88">
-        <v>70.860916076</v>
+        <v>69.00193254199998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2611420921139113</v>
+        <v>0.277706868430366</v>
       </c>
       <c r="T88">
-        <v>3.630977038143377</v>
+        <v>3.910282964154407</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05328221256528542</v>
+        <v>0.05266977334039706</v>
       </c>
       <c r="W88">
-        <v>0.2232360542771057</v>
+        <v>0.2233804674463344</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2804326977120285</v>
+        <v>0.2772093333705109</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2304428995742585</v>
+        <v>0.2323428995742585</v>
       </c>
       <c r="C89">
-        <v>-469.0257265069365</v>
+        <v>-481.3955419548183</v>
       </c>
       <c r="D89">
-        <v>326.9452734930636</v>
+        <v>324.3084580451817</v>
       </c>
       <c r="E89">
-        <v>388.171</v>
+        <v>397.904</v>
       </c>
       <c r="F89">
-        <v>846.7710000000001</v>
+        <v>856.504</v>
       </c>
       <c r="G89">
         <v>50.8</v>
@@ -8585,37 +8585,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M89">
-        <v>199.6686018</v>
+        <v>201.9636432</v>
       </c>
       <c r="N89">
-        <v>-144.3186018</v>
+        <v>-146.6136432</v>
       </c>
       <c r="O89">
-        <v>-27.42053434200001</v>
+        <v>-27.856592208</v>
       </c>
       <c r="P89">
-        <v>-116.898067458</v>
+        <v>-118.757050992</v>
       </c>
       <c r="Q89">
-        <v>69.00193254199998</v>
+        <v>67.14294900799999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.277706868430366</v>
+        <v>0.2970324407995632</v>
       </c>
       <c r="T89">
-        <v>3.910282964154407</v>
+        <v>4.236139877833941</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05266977334039706</v>
+        <v>0.05207125318880165</v>
       </c>
       <c r="W89">
-        <v>0.2233804674463344</v>
+        <v>0.2235215984980806</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2772093333705109</v>
+        <v>0.2740592273094824</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2323428995742585</v>
+        <v>0.2342428995742585</v>
       </c>
       <c r="C90">
-        <v>-481.3955419548183</v>
+        <v>-493.7231658155998</v>
       </c>
       <c r="D90">
-        <v>324.3084580451817</v>
+        <v>321.7138341844003</v>
       </c>
       <c r="E90">
-        <v>397.904</v>
+        <v>407.6370000000001</v>
       </c>
       <c r="F90">
-        <v>856.504</v>
+        <v>866.2370000000001</v>
       </c>
       <c r="G90">
         <v>50.8</v>
@@ -8667,37 +8667,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M90">
-        <v>201.9636432</v>
+        <v>204.2586846</v>
       </c>
       <c r="N90">
-        <v>-146.6136432</v>
+        <v>-148.9086846</v>
       </c>
       <c r="O90">
-        <v>-27.856592208</v>
+        <v>-28.29265007400001</v>
       </c>
       <c r="P90">
-        <v>-118.757050992</v>
+        <v>-120.616034526</v>
       </c>
       <c r="Q90">
-        <v>67.14294900799999</v>
+        <v>65.28396547399997</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2970324407995632</v>
+        <v>0.3198717535995235</v>
       </c>
       <c r="T90">
-        <v>4.236139877833941</v>
+        <v>4.621243503091572</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05207125318880165</v>
+        <v>0.05148618292825331</v>
       </c>
       <c r="W90">
-        <v>0.2235215984980806</v>
+        <v>0.2236595580655179</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2740592273094824</v>
+        <v>0.2709799101487016</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2342428995742585</v>
+        <v>0.2361428995742585</v>
       </c>
       <c r="C91">
-        <v>-493.7231658155998</v>
+        <v>-506.0096027108762</v>
       </c>
       <c r="D91">
-        <v>321.7138341844003</v>
+        <v>319.1603972891238</v>
       </c>
       <c r="E91">
-        <v>407.6370000000001</v>
+        <v>417.37</v>
       </c>
       <c r="F91">
-        <v>866.2370000000001</v>
+        <v>875.97</v>
       </c>
       <c r="G91">
         <v>50.8</v>
@@ -8749,37 +8749,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M91">
-        <v>204.2586846</v>
+        <v>206.553726</v>
       </c>
       <c r="N91">
-        <v>-148.9086846</v>
+        <v>-151.203726</v>
       </c>
       <c r="O91">
-        <v>-28.29265007400001</v>
+        <v>-28.72870794</v>
       </c>
       <c r="P91">
-        <v>-120.616034526</v>
+        <v>-122.47501806</v>
       </c>
       <c r="Q91">
-        <v>65.28396547399997</v>
+        <v>63.42498194</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3198717535995235</v>
+        <v>0.3472789289594758</v>
       </c>
       <c r="T91">
-        <v>4.621243503091572</v>
+        <v>5.08336785340073</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05148618292825331</v>
+        <v>0.0509141142290505</v>
       </c>
       <c r="W91">
-        <v>0.2236595580655179</v>
+        <v>0.2237944518647899</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2709799101487016</v>
+        <v>0.2679690222581605</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2361428995742585</v>
+        <v>0.2380428995742585</v>
       </c>
       <c r="C92">
-        <v>-506.0096027108762</v>
+        <v>-518.2558256187439</v>
       </c>
       <c r="D92">
-        <v>319.1603972891238</v>
+        <v>316.6471743812562</v>
       </c>
       <c r="E92">
-        <v>417.37</v>
+        <v>427.1030000000001</v>
       </c>
       <c r="F92">
-        <v>875.97</v>
+        <v>885.7030000000001</v>
       </c>
       <c r="G92">
         <v>50.8</v>
@@ -8831,37 +8831,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M92">
-        <v>206.553726</v>
+        <v>208.8487674</v>
       </c>
       <c r="N92">
-        <v>-151.203726</v>
+        <v>-153.4987674</v>
       </c>
       <c r="O92">
-        <v>-28.72870794</v>
+        <v>-29.16476580600001</v>
       </c>
       <c r="P92">
-        <v>-122.47501806</v>
+        <v>-124.334001594</v>
       </c>
       <c r="Q92">
-        <v>63.42498194</v>
+        <v>61.56599840599996</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3472789289594758</v>
+        <v>0.380776587732751</v>
       </c>
       <c r="T92">
-        <v>5.08336785340073</v>
+        <v>5.648186503778589</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0509141142290505</v>
+        <v>0.05035461846829169</v>
       </c>
       <c r="W92">
-        <v>0.2237944518647899</v>
+        <v>0.2239263809651768</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2679690222581605</v>
+        <v>0.265024307727851</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2380428995742585</v>
+        <v>0.2399428995742585</v>
       </c>
       <c r="C93">
-        <v>-518.2558256187439</v>
+        <v>-530.4627771099454</v>
       </c>
       <c r="D93">
-        <v>316.6471743812562</v>
+        <v>314.1732228900548</v>
       </c>
       <c r="E93">
-        <v>427.1030000000001</v>
+        <v>436.8360000000001</v>
       </c>
       <c r="F93">
-        <v>885.7030000000001</v>
+        <v>895.4360000000001</v>
       </c>
       <c r="G93">
         <v>50.8</v>
@@ -8913,37 +8913,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M93">
-        <v>208.8487674</v>
+        <v>211.1438088</v>
       </c>
       <c r="N93">
-        <v>-153.4987674</v>
+        <v>-155.7938088000001</v>
       </c>
       <c r="O93">
-        <v>-29.16476580600001</v>
+        <v>-29.60082367200001</v>
       </c>
       <c r="P93">
-        <v>-124.334001594</v>
+        <v>-126.192985128</v>
       </c>
       <c r="Q93">
-        <v>61.56599840599996</v>
+        <v>59.70701487199997</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.380776587732751</v>
+        <v>0.4226486611993449</v>
       </c>
       <c r="T93">
-        <v>5.648186503778589</v>
+        <v>6.354209816750914</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05035461846829169</v>
+        <v>0.04980728565885374</v>
       </c>
       <c r="W93">
-        <v>0.2239263809651768</v>
+        <v>0.2240554420416423</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.265024307727851</v>
+        <v>0.2621436087308092</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2399428995742585</v>
+        <v>0.2418428995742585</v>
       </c>
       <c r="C94">
-        <v>-530.4627771099454</v>
+        <v>-542.6313705265186</v>
       </c>
       <c r="D94">
-        <v>314.1732228900548</v>
+        <v>311.7376294734815</v>
       </c>
       <c r="E94">
-        <v>436.8360000000001</v>
+        <v>446.5690000000001</v>
       </c>
       <c r="F94">
-        <v>895.4360000000001</v>
+        <v>905.1690000000001</v>
       </c>
       <c r="G94">
         <v>50.8</v>
@@ -8995,37 +8995,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M94">
-        <v>211.1438088</v>
+        <v>213.4388502</v>
       </c>
       <c r="N94">
-        <v>-155.7938088000001</v>
+        <v>-158.0888502</v>
       </c>
       <c r="O94">
-        <v>-29.60082367200001</v>
+        <v>-30.03688153800001</v>
       </c>
       <c r="P94">
-        <v>-126.192985128</v>
+        <v>-128.051968662</v>
       </c>
       <c r="Q94">
-        <v>59.70701487199997</v>
+        <v>57.848031338</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4226486611993449</v>
+        <v>0.4764841842278228</v>
       </c>
       <c r="T94">
-        <v>6.354209816750914</v>
+        <v>7.26195407628676</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04980728565885374</v>
+        <v>0.04927172344746823</v>
       </c>
       <c r="W94">
-        <v>0.2240554420416423</v>
+        <v>0.224181727611087</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2621436087308092</v>
+        <v>0.2593248602498328</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2418428995742585</v>
+        <v>0.2437428995742585</v>
       </c>
       <c r="C95">
-        <v>-542.6313705265186</v>
+        <v>-554.7624911060429</v>
       </c>
       <c r="D95">
-        <v>311.7376294734815</v>
+        <v>309.3395088939572</v>
       </c>
       <c r="E95">
-        <v>446.5690000000001</v>
+        <v>456.3020000000001</v>
       </c>
       <c r="F95">
-        <v>905.1690000000001</v>
+        <v>914.9020000000002</v>
       </c>
       <c r="G95">
         <v>50.8</v>
@@ -9077,37 +9077,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M95">
-        <v>213.4388502</v>
+        <v>215.7338916</v>
       </c>
       <c r="N95">
-        <v>-158.0888502</v>
+        <v>-160.3838916000001</v>
       </c>
       <c r="O95">
-        <v>-30.03688153800001</v>
+        <v>-30.47293940400001</v>
       </c>
       <c r="P95">
-        <v>-128.051968662</v>
+        <v>-129.910952196</v>
       </c>
       <c r="Q95">
-        <v>57.848031338</v>
+        <v>55.98904780399997</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4764841842278228</v>
+        <v>0.5482648815991268</v>
       </c>
       <c r="T95">
-        <v>7.26195407628676</v>
+        <v>8.472279755667889</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04927172344746823</v>
+        <v>0.04874755617675047</v>
       </c>
       <c r="W95">
-        <v>0.224181727611087</v>
+        <v>0.2243053262535223</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2593248602498328</v>
+        <v>0.2565660851407919</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2437428995742585</v>
+        <v>0.2456428995742585</v>
       </c>
       <c r="C96">
-        <v>-554.7624911060429</v>
+        <v>-566.8569970543897</v>
       </c>
       <c r="D96">
-        <v>309.3395088939572</v>
+        <v>306.9780029456103</v>
       </c>
       <c r="E96">
-        <v>456.3020000000001</v>
+        <v>466.0350000000001</v>
       </c>
       <c r="F96">
-        <v>914.9020000000002</v>
+        <v>924.6350000000001</v>
       </c>
       <c r="G96">
         <v>50.8</v>
@@ -9159,37 +9159,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M96">
-        <v>215.7338916</v>
+        <v>218.028933</v>
       </c>
       <c r="N96">
-        <v>-160.3838916000001</v>
+        <v>-162.678933</v>
       </c>
       <c r="O96">
-        <v>-30.47293940400001</v>
+        <v>-30.90899727000001</v>
       </c>
       <c r="P96">
-        <v>-129.910952196</v>
+        <v>-131.76993573</v>
       </c>
       <c r="Q96">
-        <v>55.98904780399997</v>
+        <v>54.13006426999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5482648815991268</v>
+        <v>0.6487578579189524</v>
       </c>
       <c r="T96">
-        <v>8.472279755667889</v>
+        <v>10.16673570680147</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04874755617675047</v>
+        <v>0.04823442400646889</v>
       </c>
       <c r="W96">
-        <v>0.2243053262535223</v>
+        <v>0.2244263228192746</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2565660851407919</v>
+        <v>0.253865389507731</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2456428995742585</v>
+        <v>0.2475428995742585</v>
       </c>
       <c r="C97">
-        <v>-566.8569970543897</v>
+        <v>-578.9157205697093</v>
       </c>
       <c r="D97">
-        <v>306.9780029456103</v>
+        <v>304.6522794302909</v>
       </c>
       <c r="E97">
-        <v>466.0350000000001</v>
+        <v>475.7680000000001</v>
       </c>
       <c r="F97">
-        <v>924.6350000000001</v>
+        <v>934.3680000000002</v>
       </c>
       <c r="G97">
         <v>50.8</v>
@@ -9241,37 +9241,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M97">
-        <v>218.028933</v>
+        <v>220.3239744000001</v>
       </c>
       <c r="N97">
-        <v>-162.678933</v>
+        <v>-164.9739744000001</v>
       </c>
       <c r="O97">
-        <v>-30.90899727000001</v>
+        <v>-31.34505513600001</v>
       </c>
       <c r="P97">
-        <v>-131.76993573</v>
+        <v>-133.628919264</v>
       </c>
       <c r="Q97">
-        <v>54.13006426999999</v>
+        <v>52.27108073599996</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6487578579189524</v>
+        <v>0.7994973223986909</v>
       </c>
       <c r="T97">
-        <v>10.16673570680147</v>
+        <v>12.70841963350185</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04823442400646889</v>
+        <v>0.04773198208973484</v>
       </c>
       <c r="W97">
-        <v>0.2244263228192746</v>
+        <v>0.2245447986232405</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.253865389507731</v>
+        <v>0.2512209583670254</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2475428995742585</v>
+        <v>0.2494428995742585</v>
       </c>
       <c r="C98">
-        <v>-578.915720569709</v>
+        <v>-590.9394688202193</v>
       </c>
       <c r="D98">
-        <v>304.6522794302911</v>
+        <v>302.3615311797807</v>
       </c>
       <c r="E98">
-        <v>475.768</v>
+        <v>485.501</v>
       </c>
       <c r="F98">
-        <v>934.3680000000001</v>
+        <v>944.101</v>
       </c>
       <c r="G98">
         <v>50.8</v>
@@ -9323,37 +9323,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M98">
-        <v>220.3239744</v>
+        <v>222.6190158</v>
       </c>
       <c r="N98">
-        <v>-164.9739744</v>
+        <v>-167.2690158</v>
       </c>
       <c r="O98">
-        <v>-31.34505513600001</v>
+        <v>-31.781113002</v>
       </c>
       <c r="P98">
-        <v>-133.628919264</v>
+        <v>-135.487902798</v>
       </c>
       <c r="Q98">
-        <v>52.27108073599999</v>
+        <v>50.41209720200001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7994973223986889</v>
+        <v>1.050729763198252</v>
       </c>
       <c r="T98">
-        <v>12.70841963350181</v>
+        <v>16.94455951133575</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04773198208973484</v>
+        <v>0.04723989980014995</v>
       </c>
       <c r="W98">
-        <v>0.2245447986232405</v>
+        <v>0.2246608316271246</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2512209583670255</v>
+        <v>0.2486310515797366</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2494428995742585</v>
+        <v>0.2513428995742585</v>
       </c>
       <c r="C99">
-        <v>-590.9394688202193</v>
+        <v>-602.9290248782121</v>
       </c>
       <c r="D99">
-        <v>302.3615311797807</v>
+        <v>300.104975121788</v>
       </c>
       <c r="E99">
-        <v>485.501</v>
+        <v>495.234</v>
       </c>
       <c r="F99">
-        <v>944.101</v>
+        <v>953.8340000000001</v>
       </c>
       <c r="G99">
         <v>50.8</v>
@@ -9405,37 +9405,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M99">
-        <v>222.6190158</v>
+        <v>224.9140572</v>
       </c>
       <c r="N99">
-        <v>-167.2690158</v>
+        <v>-169.5640572</v>
       </c>
       <c r="O99">
-        <v>-31.781113002</v>
+        <v>-32.217170868</v>
       </c>
       <c r="P99">
-        <v>-135.487902798</v>
+        <v>-137.346886332</v>
       </c>
       <c r="Q99">
-        <v>50.41209720200001</v>
+        <v>48.55311366799998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.050729763198252</v>
+        <v>1.553194644797378</v>
       </c>
       <c r="T99">
-        <v>16.94455951133575</v>
+        <v>25.41683926700362</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04723989980014995</v>
+        <v>0.04675786000627086</v>
       </c>
       <c r="W99">
-        <v>0.2246608316271246</v>
+        <v>0.2247744966105213</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2486310515797366</v>
+        <v>0.2460940000330045</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2513428995742585</v>
+        <v>0.2532428995742585</v>
       </c>
       <c r="C100">
-        <v>-602.9290248782121</v>
+        <v>-614.8851486125429</v>
       </c>
       <c r="D100">
-        <v>300.104975121788</v>
+        <v>297.8818513874571</v>
       </c>
       <c r="E100">
-        <v>495.234</v>
+        <v>504.967</v>
       </c>
       <c r="F100">
-        <v>953.8340000000001</v>
+        <v>963.567</v>
       </c>
       <c r="G100">
         <v>50.8</v>
@@ -9487,37 +9487,37 @@
         <v>55.34999999999999</v>
       </c>
       <c r="M100">
-        <v>224.9140572</v>
+        <v>227.2090986</v>
       </c>
       <c r="N100">
-        <v>-169.5640572</v>
+        <v>-171.8590986</v>
       </c>
       <c r="O100">
-        <v>-32.217170868</v>
+        <v>-32.653228734</v>
       </c>
       <c r="P100">
-        <v>-137.346886332</v>
+        <v>-139.205869866</v>
       </c>
       <c r="Q100">
-        <v>48.55311366799998</v>
+        <v>46.69413013400001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.553194644797378</v>
+        <v>3.060589289594756</v>
       </c>
       <c r="T100">
-        <v>25.41683926700362</v>
+        <v>50.83367853400725</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04675786000627086</v>
+        <v>0.04628555839004592</v>
       </c>
       <c r="W100">
-        <v>0.2247744966105213</v>
+        <v>0.2248858653316272</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2460940000330045</v>
+        <v>0.2436082020528733</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2532428995742585</v>
-      </c>
-      <c r="C101">
-        <v>-614.8851486125429</v>
-      </c>
-      <c r="D101">
-        <v>297.8818513874571</v>
-      </c>
-      <c r="E101">
-        <v>504.967</v>
-      </c>
-      <c r="F101">
-        <v>963.567</v>
-      </c>
-      <c r="G101">
-        <v>50.8</v>
-      </c>
-      <c r="H101">
-        <v>514.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>241.25</v>
-      </c>
-      <c r="K101">
-        <v>185.9</v>
-      </c>
-      <c r="L101">
-        <v>55.34999999999999</v>
-      </c>
-      <c r="M101">
-        <v>227.2090986</v>
-      </c>
-      <c r="N101">
-        <v>-171.8590986</v>
-      </c>
-      <c r="O101">
-        <v>-32.653228734</v>
-      </c>
-      <c r="P101">
-        <v>-139.205869866</v>
-      </c>
-      <c r="Q101">
-        <v>46.69413013400001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.060589289594756</v>
-      </c>
-      <c r="T101">
-        <v>50.83367853400725</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04628555839004592</v>
-      </c>
-      <c r="W101">
-        <v>0.2248858653316272</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2436082020528733</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
